--- a/Petty cash for proposal.xlsx
+++ b/Petty cash for proposal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16600" windowHeight="17020" firstSheet="2"/>
+    <workbookView windowWidth="16000" windowHeight="17020" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Petty Cash Andika" sheetId="34" r:id="rId1"/>
@@ -26,12 +26,8 @@
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>Tanggal</t>
   </si>
@@ -93,161 +89,179 @@
     <t>DEPT. TOTAL :</t>
   </si>
   <si>
+    <t>KEMFOOD BALI</t>
+  </si>
+  <si>
+    <t>PURCHASE SALAMI 1 KG</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>TRANSFER KE OLMEC INDUSTRIES INDONESIA PT</t>
+  </si>
+  <si>
+    <t>PURCHASE NACHOS 2 PAX</t>
+  </si>
+  <si>
+    <t>KIMMY LISTRIK</t>
+  </si>
+  <si>
+    <t>PURCHASE TRAVO FOR BAR LED LIGHTS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>TRANSFER KE LADANG ROTI KREATIF PT</t>
+  </si>
+  <si>
+    <t>PAYMENT TO BRAUD FOR BREAD ORDER</t>
+  </si>
+  <si>
+    <t>BANK BRI</t>
+  </si>
+  <si>
+    <t>TOPPED UP RP. 3.000.000</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>OVO ADMIN FEE</t>
+  </si>
+  <si>
+    <t>ADMIN FEE RP. 1.200</t>
+  </si>
+  <si>
+    <t>TRANSFER KE KADEK ANDIKA PUTRA</t>
+  </si>
+  <si>
+    <t>REIMBURSE DOWNPAYMENT OF HADYMAN FOR BAR CEILLING WORK TO ANDIKA PURCHASING</t>
+  </si>
+  <si>
+    <t>TRANSFER KE DINETA JAYA PT</t>
+  </si>
+  <si>
+    <t>PAYMENT FOR 3 PCS OF 1 KG OF SOUR CREAM TO DINETA JAYA</t>
+  </si>
+  <si>
+    <t>DEWATA INDAH</t>
+  </si>
+  <si>
+    <t>PURCHASE 4 PCS OF PLANTS</t>
+  </si>
+  <si>
+    <t>ANNA FLORIST, JLNRAYA ULU</t>
+  </si>
+  <si>
+    <t>PURCHASE FLOWERS FOR FLOOR</t>
+  </si>
+  <si>
+    <t>CM ULUWATU</t>
+  </si>
+  <si>
+    <t>REPAYMENT ACTION FOR STUCKED TRANSACTIONS REFERRING TO 11TH OF JANUARY 2026 PENDING PAYMENT TRANSACTION TO PURCHASE HAIRNET AND MASKER FOR HACCP INSPECTIONS TO CLAIM MY PERSONAL COLLATERAL CASH MONEY.</t>
+  </si>
+  <si>
+    <t>PURCHASE 3 PCS OF KEBAB STICKS</t>
+  </si>
+  <si>
+    <t>JANUARY</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>JIMBARAN BARU ULUWATU</t>
+  </si>
+  <si>
+    <t>PURCHASE DOOR HINGE</t>
+  </si>
+  <si>
+    <t>PAYMENT OF 2 PCS OF NAPKIN ROLL</t>
+  </si>
+  <si>
+    <t>PURCHASE 4 PCS TORTILLA WRAP AT EL TORTILLA</t>
+  </si>
+  <si>
     <t>TOKOPEDIA</t>
   </si>
   <si>
-    <t>PURCHASE 12 PCS OF SAUCE DISH FROM TOKOPEDIA</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>BANK BRI</t>
-  </si>
-  <si>
-    <t>TOPPED UP RP. 3.000.000</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>OVO ADMIN FEE</t>
-  </si>
-  <si>
-    <t>ADMIN FEE RP. 1.200</t>
-  </si>
-  <si>
-    <t>TRANSFER KE LADANG ROTI KREATIF PT</t>
-  </si>
-  <si>
-    <t>PURCHASE BREAD FROM BRAUD W OVO</t>
-  </si>
-  <si>
-    <t>PURCHASE 100 PCS OF BAMBOO STRAW FROM TOKOPEDIA W OVO</t>
+    <t>PURCHASE DEXTONE EPOXY GLUE 48 GR</t>
+  </si>
+  <si>
+    <t>PURCHASE 4 PACKS OF TORTILLA WRAP AT EL TORTILLA</t>
+  </si>
+  <si>
+    <t>MR.D.I.Y RK JIMBARAN</t>
+  </si>
+  <si>
+    <t>PURCHASE 3 PACKS OF  WHITE BOARD MARKER</t>
+  </si>
+  <si>
+    <t>ARTHAYASA PHOTO HO</t>
+  </si>
+  <si>
+    <t>PURCHASE 1 BOX OF STAPLES REFILL FOR FLOOR</t>
+  </si>
+  <si>
+    <t>SURYA JAYA ELEKTRIK HO</t>
+  </si>
+  <si>
+    <t>PURCHASE CUSTOM MADE ELECTRICAL SOCKET 15 METER CABLE LENGTH</t>
+  </si>
+  <si>
+    <t>TRANSFER KE NI LUH MULIA DEWI</t>
+  </si>
+  <si>
+    <t>PAYMENT TO MULIA JAYA FOR PASSION FRUIT</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>TRANSFER KE SDRI CINDY FITRIA CAHYANI</t>
-  </si>
-  <si>
-    <t>REIMBURSE PAYMENT FOR AICE STRAWBERRY ICE CREAM TO CINDY FLOOR</t>
-  </si>
-  <si>
-    <t>MR.D.I.Y RK JIMBARAN</t>
-  </si>
-  <si>
-    <t>PURCHASE STRONGER TAPE AND DOUBLE TAPE</t>
-  </si>
-  <si>
-    <t>ANNA FLORIST, JLNRAYA ULU</t>
-  </si>
-  <si>
-    <t>PURCHASE FLOWERS FOR FLOOW</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>SURYA JAYA ELEKTRIK HO</t>
-  </si>
-  <si>
-    <t>PURCHASE 2 METER CABLE TO FIX COFFEE MACHINE ELECTRICITY</t>
-  </si>
-  <si>
-    <t>PURCHASE 2 PCS OF MAGNETIC KITCHEN TIMER</t>
+    <t>REFUND TOKOPEDIA CANCELLED TRANSACTIONS BY SELLER (REFERENCE: 6 FEB 2026 PURCHASE DEXTONE EPOXY GLUE 48 GR)</t>
+  </si>
+  <si>
+    <t>MITRA 10 GATSU, BALI</t>
+  </si>
+  <si>
+    <t>PURCHASE 4 PCS OF DEXTONE EPOXY GLUE 48 GR TO FIX RESTAURANT TABLE</t>
+  </si>
+  <si>
+    <t>TRANSFER KE I WAYAN GEDE SUDIARTHA S</t>
+  </si>
+  <si>
+    <t>PURCHASE OF NAILS TO FIX KITCHEN DOOR</t>
   </si>
   <si>
     <t>TRANSFER KE LUH DINA ANGGRA WAHY</t>
   </si>
   <si>
-    <t>REIMBURSE PURCHASE OF BALINESE OFFERING TO DINA FLOOR</t>
-  </si>
-  <si>
-    <t>PURCHASE MOUSE AND INSECT TRAPPER FOR BAR ON TOKOPEDIA</t>
-  </si>
-  <si>
-    <t>BSM PRINTING BALI</t>
-  </si>
-  <si>
-    <t>PRINT FLOOR COFFEE MESAGES</t>
-  </si>
-  <si>
-    <t>PURCHASE STORAGE CONTAINER FOR WHEY PROTEIN AND 2 PCS OF TOILET FRESHNER</t>
-  </si>
-  <si>
-    <t>TRANSFER KE LILIEK DWIWAHJUNING</t>
-  </si>
-  <si>
-    <t>PURCHASE MEDICINAL SUPPLIES FOR FLOOR</t>
-  </si>
-  <si>
-    <t>TOKO BINTANG 01</t>
-  </si>
-  <si>
-    <t>PURCHASE PAPER TAPE FOR BAR</t>
-  </si>
-  <si>
-    <t>SINAR MULIA FOTOKOPI</t>
-  </si>
-  <si>
-    <t>PRINT EDIBLE PAPER 2 SHEET</t>
-  </si>
-  <si>
-    <t>PEPITO EXPRESS PECATU</t>
-  </si>
-  <si>
-    <t>PURCHASE GLUTEN FREE SPAGHETTI</t>
-  </si>
-  <si>
-    <t>TRANSFER KE HANTAR PRADA HARMONI PT</t>
-  </si>
-  <si>
-    <t>PURCHASE MATERIALS TO REPAIR BAR CEILLING</t>
-  </si>
-  <si>
-    <t>OVO</t>
-  </si>
-  <si>
-    <t>QRIS CORRECTION FOR 12TH JANUARY STUCK ON PAYMENT TRANSACTION MONEY GOT RETURNED</t>
-  </si>
-  <si>
-    <t>KEMFOOD BALI</t>
-  </si>
-  <si>
-    <t>PURCHASE SALAMI 1 KG</t>
-  </si>
-  <si>
-    <t>TRANSFER KE OLMEC INDUSTRIES INDONESIA PT</t>
-  </si>
-  <si>
-    <t>PURCHASE NACHOS 2 PAX</t>
-  </si>
-  <si>
-    <t>KIMMY LISTRIK</t>
-  </si>
-  <si>
-    <t>PURCHASE TRAVO FOR BAR LED LIGHTS</t>
-  </si>
-  <si>
-    <t>PAYMENT TO BRAUD FOR BREAD ORDER</t>
-  </si>
-  <si>
-    <t>BUNGA OVO NABUNG (REWARDS)</t>
-  </si>
-  <si>
-    <t>RECEIVED INTEREST FROM OVO SAVINGS</t>
-  </si>
-  <si>
-    <t>I</t>
+    <t>REIMBURSE FLOOR BALINESE OFFERING TO DINA FLOOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAYMENT FOR BRAUD BREAD </t>
+  </si>
+  <si>
+    <t>1ST ATTEMPT ON PURCHASE OF TORTILLA FAILED AND RESULTING IN PENDING PAYMENT.</t>
+  </si>
+  <si>
+    <t>PURCHASE OF TORTILLA</t>
+  </si>
+  <si>
+    <t>PURCHASE FLOOR FLOWER</t>
+  </si>
+  <si>
+    <t>FEBRUARY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -256,8 +270,9 @@
     <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@"/>
     <numFmt numFmtId="182" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="183" formatCode="dd\-mmm\-yy"/>
+    <numFmt numFmtId="184" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,6 +330,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -494,13 +517,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -691,7 +714,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -883,6 +906,19 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
@@ -1010,137 +1046,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1210,46 +1246,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="182" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1264,14 +1333,29 @@
     <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1559,33 +1643,149 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>24765</xdr:colOff>
+      <xdr:colOff>35877</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>27305</xdr:rowOff>
+      <xdr:rowOff>24447</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2205355</xdr:colOff>
+      <xdr:colOff>2189797</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>2942590</xdr:rowOff>
+      <xdr:rowOff>1386522</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="ID_3D067219B2CB4115928E4E0DCCFDA226"/>
+        <xdr:cNvPr id="7" name="ID_F0AC9804840F4BB9BB272032208A820C" descr="PHOTO-2026-01-28-10-32-20"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
+        <a:srcRect t="7965" b="5200"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="12368530" y="637540"/>
+          <a:ext cx="1362075" cy="2153920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>29527</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>24447</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2196782</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1398587</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="ID_F71D9C669D8C4463B4C7EEA86E536043" descr="PHOTO-2026-01-28-11-08-21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect t="8832"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="12362815" y="2045335"/>
+          <a:ext cx="1374140" cy="2167255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>39052</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2186622</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1263967</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="ID_9A15E299FC5845389941E72A5069E4F8" descr="PHOTO-2026-01-28-12-12-05"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="12429490" y="3399790"/>
+          <a:ext cx="1240155" cy="2147570"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>33020</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2193290</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1447800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="ID_EC0844A916624A2F93221FEB4CD1F711"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962130" y="1036955"/>
-          <a:ext cx="2180590" cy="2915285"/>
+          <a:off x="11970385" y="5142865"/>
+          <a:ext cx="2160270" cy="1423035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1602,33 +1802,344 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>35560</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2190750</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1009650</xdr:rowOff>
+      <xdr:colOff>2192020</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1005840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="ID_7374697EE26B4D18B861BDB79C3811C4" descr="PHOTO-2026-01-21-20-25-33"/>
+        <xdr:cNvPr id="11" name="ID_BCA39D04776E45DF855A9B725BB0F766" descr="PHOTO-2026-01-30-13-56-39"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect t="6169" b="53182"/>
+        <a:blip r:embed="rId5"/>
+        <a:srcRect t="6129" b="53832"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11972925" y="3994150"/>
-          <a:ext cx="2155190" cy="2001520"/>
+          <a:off x="11972925" y="6606540"/>
+          <a:ext cx="2156460" cy="1998980"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2197735</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1599565</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="ID_94E360EC8BCA433DB3C759F952108DD8" descr="PHOTO-2026-01-30-15-46-11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:srcRect l="9895" t="19029" r="9927" b="5568"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11967845" y="13568045"/>
+          <a:ext cx="2167255" cy="1576705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>23495</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>35560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2204720</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>4902200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="ID_402A5938337645BC98F954A6E7617C29" descr="PHOTO-2026-01-30-13-27-45"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:srcRect t="3756" b="33327"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11960860" y="8651240"/>
+          <a:ext cx="2181225" cy="4866640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>23495</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2204720</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3135630</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="ID_5DA81C62E9EF4E60A048CA21F1DC9AEC" descr="PHOTO-2026-01-31-10-00-42"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:srcRect b="22372"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11960860" y="15193010"/>
+          <a:ext cx="2181225" cy="3105150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>26670</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2201545</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>2690495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="ID_5CEAC97CD50F456BAA51F453804F75F0" descr="PHOTO-2026-01-31-10-52-44"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:srcRect t="33077"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11964035" y="18336260"/>
+          <a:ext cx="2174875" cy="2667635"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>369570</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1858010</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>5184775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="ID_A1FEAEBC090D4B3BB742BD19E2FE29C4" descr="PHOTO-2026-01-31-11-09-00"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:srcRect t="2904" b="25044"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12306935" y="21052790"/>
+          <a:ext cx="1488440" cy="5161915"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2202180</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>2399030</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="ID_9C36C34BF19A4EB3BC7BCB206F270E3F" descr="PHOTO-2026-01-31-11-11-45"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:srcRect t="4299" b="36109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11962765" y="26253440"/>
+          <a:ext cx="2176780" cy="2376170"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>24765</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2203450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3458845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="ID_FC1087157EAD4FE2A7963D7B42004ECE" descr="PHOTO-2026-02-01-15-14-44"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:srcRect b="17058"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11962130" y="28675965"/>
+          <a:ext cx="2178685" cy="3432175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2198370</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1365250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="ID_2BCA740AFE064935A5806840BB1E9367" descr="PHOTO-2026-02-02-13-42-36"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11967845" y="32157670"/>
+          <a:ext cx="2167890" cy="1341755"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1641,33 +2152,33 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>24765</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36195</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2193925</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1398270</xdr:rowOff>
+      <xdr:colOff>2202815</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2940050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="ID_12E71CBAD00543749784EF72AB320772" descr="PHOTO-2026-01-21-17-50-31"/>
+        <xdr:cNvPr id="20" name="ID_F0A27C0ABDA846ABB27C587C95EC34D0" descr="PHOTO-2026-02-06-15-16-59"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:srcRect l="6551" t="11616" b="3472"/>
+        <a:blip r:embed="rId14"/>
+        <a:srcRect b="28638"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12363450" y="5632450"/>
-          <a:ext cx="1373505" cy="2162175"/>
+        <a:xfrm>
+          <a:off x="11969115" y="50175160"/>
+          <a:ext cx="2171065" cy="2903855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1679,77 +2190,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>33020</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>24765</xdr:rowOff>
+      <xdr:colOff>29845</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2193925</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>3053715</xdr:rowOff>
+      <xdr:colOff>2193290</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1400175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="126" name="ID_A99F17B4EA444FC6B05756FCD97FE8CF"/>
+        <xdr:cNvPr id="21" name="ID_AD1042828E374395ACC38CF1834F1462" descr="PHOTO-2026-02-03-14-12-48"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect b="36929"/>
+        <a:blip r:embed="rId15"/>
+        <a:srcRect t="8031"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11970385" y="7441565"/>
-          <a:ext cx="2160905" cy="3028950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>76835</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>21590</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2155825</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>5184775</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="127" name="ID_B42ACF0736B1474B892B8459126013C1" descr="PHOTO-2026-01-23-10-58-25"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect l="13090" t="5146" r="19160" b="5529"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12014200" y="11974195"/>
-          <a:ext cx="2078990" cy="5163185"/>
+        <a:xfrm rot="16200000">
+          <a:off x="12362180" y="33143825"/>
+          <a:ext cx="1373505" cy="2163445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1761,34 +2229,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>28892</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>21272</xdr:rowOff>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>32385</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2203767</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>1456372</xdr:rowOff>
+      <xdr:colOff>2197735</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>3620135</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="128" name="ID_333B7D9A1DF04759BA6EFE4776B15000" descr="PHOTO-2026-01-22-15-45-47"/>
+        <xdr:cNvPr id="22" name="ID_72F5A7BAB5AE4EB98FA06D9EB701C540" descr="PHOTO-2026-02-06-09-07-20"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:srcRect t="16165"/>
+        <a:blip r:embed="rId16"/>
+        <a:srcRect t="21456" b="6921"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12335510" y="10134600"/>
-          <a:ext cx="1435100" cy="2174875"/>
+        <a:xfrm>
+          <a:off x="11963400" y="34958655"/>
+          <a:ext cx="2171700" cy="3587750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1800,34 +2268,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>24765</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>48577</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>25717</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2204720</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>3425825</xdr:rowOff>
+      <xdr:colOff>2174557</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1248092</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="129" name="ID_B8BEE2BA4320446EAE67F7D50C62E987" descr="PHOTO-2026-01-23-13-20-31"/>
+        <xdr:cNvPr id="23" name="ID_43FFD2933CBD452EAB495FF2A9CFB257" descr="PHOTO-2026-02-06-11-36-47"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:srcRect t="10777" r="6433" b="11553"/>
+        <a:blip r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11962130" y="19876770"/>
-          <a:ext cx="2179955" cy="3400425"/>
+        <a:xfrm rot="16200000">
+          <a:off x="12437110" y="38153975"/>
+          <a:ext cx="1222375" cy="2125980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1839,34 +2306,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>24765</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>40005</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2204720</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>2681605</xdr:rowOff>
+      <xdr:colOff>2197735</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>4025265</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="130" name="ID_2D158377CEDF4284A2F98F3B855ADD63" descr="PHOTO-2026-01-23-11-20-25"/>
+        <xdr:cNvPr id="24" name="ID_63F3B46FF3854C948831037D58655375" descr="PHOTO-2026-02-06-12-45-45"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:srcRect t="17014" b="16742"/>
+        <a:blip r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962130" y="17179925"/>
-          <a:ext cx="2179955" cy="2654935"/>
+          <a:off x="11963400" y="39902765"/>
+          <a:ext cx="2171700" cy="3985260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1878,34 +2344,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>22225</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>33020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2208530</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>5088255</xdr:rowOff>
+      <xdr:colOff>2197735</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2892425</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="131" name="ID_B9751EE8515543B5B8041F0E265FA4C0" descr="PHOTO-2026-01-25-15-18-21"/>
+        <xdr:cNvPr id="25" name="ID_F97F2F063AF548E19B5243CED2218331" descr="PHOTO-2026-02-06-12-54-09"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:srcRect l="14491" t="6351" r="9789"/>
+        <a:blip r:embed="rId19"/>
+        <a:srcRect b="28217"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11959590" y="38640385"/>
-          <a:ext cx="2186305" cy="5060315"/>
+          <a:off x="11963400" y="43953430"/>
+          <a:ext cx="2171700" cy="2859405"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1917,34 +2383,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>22225</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>33655</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2208530</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>4822825</xdr:rowOff>
+      <xdr:colOff>2197735</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>3275330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="132" name="ID_245A041C66A84E8E9174AE507C4CC7CD" descr="PHOTO-2026-01-25-10-20-54"/>
+        <xdr:cNvPr id="26" name="ID_E598DCBE7B4B46E6B40DA849DD060CEF" descr="PHOTO-2026-02-06-13-20-21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:srcRect l="8652" r="5947"/>
+        <a:blip r:embed="rId20"/>
+        <a:srcRect l="4154" t="6903" b="15133"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11959590" y="33806765"/>
-          <a:ext cx="2186305" cy="4788535"/>
+          <a:off x="11963400" y="46869350"/>
+          <a:ext cx="2171700" cy="3241675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1956,34 +2422,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>29210</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
+      <xdr:colOff>23495</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2200910</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>2997200</xdr:rowOff>
+      <xdr:colOff>2207260</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>3328670</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="133" name="ID_956AF2A1877046F9B476A44FF490E10B" descr="PHOTO-2026-01-25-09-18-23"/>
+        <xdr:cNvPr id="27" name="ID_6545CE772D0C4FD68085584DF2013A8B" descr="PHOTO-2026-02-07-11-42-00"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:srcRect t="5315" b="36253"/>
+        <a:blip r:embed="rId21"/>
+        <a:srcRect b="19481"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11966575" y="30784800"/>
-          <a:ext cx="2171700" cy="2974975"/>
+          <a:off x="11960860" y="61436885"/>
+          <a:ext cx="2183765" cy="3302000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1995,34 +2461,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>22225</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2208530</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>3201670</xdr:rowOff>
+      <xdr:colOff>2204720</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>3009265</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="134" name="ID_F7D0A981F19946699D593433DA887FE4" descr="PHOTO-2026-01-24-19-20-29"/>
+        <xdr:cNvPr id="28" name="ID_A014566F8AB34DC7AA4922F2DC77588C" descr="PHOTO-2026-02-07-18-29-38"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:srcRect t="19446" b="3501"/>
+        <a:blip r:embed="rId22"/>
+        <a:srcRect b="27001"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11959590" y="27577415"/>
-          <a:ext cx="2186305" cy="3173730"/>
+          <a:off x="11963400" y="64780160"/>
+          <a:ext cx="2178685" cy="2985770"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2034,34 +2500,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>22225</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>29845</xdr:rowOff>
+      <xdr:colOff>143510</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2208530</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>4229100</xdr:rowOff>
+      <xdr:colOff>2087245</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>5181600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="135" name="ID_F0CBAE507C0C498DB2D88667E25ABD31" descr="PHOTO-2026-01-24-15-20-04"/>
+        <xdr:cNvPr id="29" name="ID_D3284D46A7454CCA91806A85F05EAA6D" descr="PHOTO-2026-02-07-01-33-21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:srcRect t="12627" b="7399"/>
+        <a:blip r:embed="rId23"/>
+        <a:srcRect t="5251" b="984"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11959590" y="23333075"/>
-          <a:ext cx="2186305" cy="4199255"/>
+          <a:off x="12080875" y="53123465"/>
+          <a:ext cx="1943735" cy="5158105"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2074,33 +2540,33 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2206625</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>3439795</xdr:rowOff>
+      <xdr:colOff>2205355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3086735</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="136" name="ID_BFC0B4C918D54E76A83BB6D225765B1B" descr="PHOTO-2026-01-26-16-47-48"/>
+        <xdr:cNvPr id="30" name="ID_1075E92F8AD74260B59D72F79C7ADE65" descr="PHOTO-2026-02-07-09-35-42"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:srcRect t="14891"/>
+        <a:blip r:embed="rId24"/>
+        <a:srcRect t="4110" b="17594"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962765" y="43756580"/>
-          <a:ext cx="2181225" cy="3409315"/>
+          <a:off x="11962765" y="58324115"/>
+          <a:ext cx="2179955" cy="3063240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2112,34 +2578,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>346710</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2206625</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>2632075</xdr:rowOff>
+      <xdr:colOff>1887220</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>5188585</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="137" name="ID_C417BE0AB9B444559509EF3782D31188" descr="PHOTO-2026-01-26-17-02-30"/>
+        <xdr:cNvPr id="3" name="ID_CB24E0A27A784928BCFF986663BAB11D" descr="PHOTO-2026-02-08-15-26-12"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
-        <a:srcRect t="11806" b="23131"/>
+        <a:blip r:embed="rId25"/>
+        <a:srcRect t="4009" b="3497"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962765" y="47210345"/>
-          <a:ext cx="2181225" cy="2606675"/>
+          <a:off x="12284075" y="67814190"/>
+          <a:ext cx="1540510" cy="5164455"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2151,34 +2617,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>26670</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>30797</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>26352</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2205355</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2735580</xdr:rowOff>
+      <xdr:colOff>2194242</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1408112</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="138" name="ID_FD98B745FC8A4146A66BE675A98402D9" descr="PHOTO-2026-01-27-09-51-33"/>
+        <xdr:cNvPr id="2" name="ID_7BE29291E98642E3B1A4501AE281BC5E" descr="PHOTO-2026-02-10-09-59-11"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:srcRect t="17454" b="14801"/>
+        <a:blip r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11964035" y="49857660"/>
-          <a:ext cx="2178685" cy="2710180"/>
+        <a:xfrm rot="16200000">
+          <a:off x="12358370" y="77826235"/>
+          <a:ext cx="1381760" cy="2163445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2190,34 +2655,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2206625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>3506470</xdr:rowOff>
+      <xdr:colOff>2174875</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>5179060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="139" name="ID_2DC64C60B1554DCD90B294F546C4AC3D" descr="PHOTO-2026-01-27-10-57-33"/>
+        <xdr:cNvPr id="4" name="ID_58CC131D1A9A46F5A8657188A51A6CD1" descr="PHOTO-2026-02-10-14-42-00"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId17"/>
-        <a:srcRect t="10916" b="2205"/>
+        <a:blip r:embed="rId27"/>
+        <a:srcRect t="3630" b="31770"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962765" y="52616100"/>
-          <a:ext cx="2181225" cy="3477260"/>
+          <a:off x="11994515" y="73014205"/>
+          <a:ext cx="2117725" cy="5155565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2229,270 +2694,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>31115</xdr:rowOff>
+      <xdr:colOff>24130</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2208530</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>4781550</xdr:rowOff>
+      <xdr:colOff>2207895</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>2573020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="140" name="ID_3BF2286560114684934F6D4A8492B971" descr="PHOTO-2026-01-27-15-57-50"/>
+        <xdr:cNvPr id="5" name="ID_B5E07496F2BE43EEB6633AE6D770ABED" descr="PHOTO-2026-02-10-10-52-35"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId18"/>
-        <a:srcRect l="16157" t="8384" r="9143" b="6079"/>
+        <a:blip r:embed="rId28"/>
+        <a:srcRect t="35309" b="1219"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962765" y="56145430"/>
-          <a:ext cx="2183130" cy="4750435"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>35877</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>24447</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2189797</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>1386522</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_F0AC9804840F4BB9BB272032208A820C" descr="PHOTO-2026-01-28-10-32-20"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId19"/>
-        <a:srcRect t="7965" b="5200"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12368530" y="65615185"/>
-          <a:ext cx="1362075" cy="2153920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>24765</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>41275</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2202180</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>5032375</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_7E9C31DE4CB94F31B1D70E741E7040E9" descr="PHOTO-2026-01-28-16-53-44"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId20"/>
-        <a:srcRect t="4735"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11962130" y="60963810"/>
-          <a:ext cx="2177415" cy="4991100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>29527</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>24447</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2196782</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1398587</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_F71D9C669D8C4463B4C7EEA86E536043" descr="PHOTO-2026-01-28-11-08-21"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId21"/>
-        <a:srcRect t="8832"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12362815" y="67022980"/>
-          <a:ext cx="1374140" cy="2167255"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>39052</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2186622</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1263967</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_9A15E299FC5845389941E72A5069E4F8" descr="PHOTO-2026-01-28-12-12-05"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12429490" y="68377435"/>
-          <a:ext cx="1240155" cy="2147570"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>33020</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>24765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2193290</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1447800</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_EC0844A916624A2F93221FEB4CD1F711"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11970385" y="70120510"/>
-          <a:ext cx="2160270" cy="1423035"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>24130</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2209800</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>3656965</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="ID_89C0901F4E4F4DED90D7A8C4D67B2E76" descr="PHOTO-2026-01-28-17-33-06"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId24"/>
-        <a:srcRect t="5328" b="21976"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11961495" y="71587995"/>
-          <a:ext cx="2185670" cy="3630295"/>
+          <a:off x="11961495" y="79637255"/>
+          <a:ext cx="2183765" cy="2549525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2762,7 +2991,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BE837"/>
+  <dimension ref="A1:BE812"/>
   <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -2810,77 +3039,77 @@
       <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N1" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="40" t="s">
+      <c r="P1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="Q1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="42"/>
-      <c r="AH1" s="42"/>
-      <c r="AI1" s="42"/>
-      <c r="AJ1" s="42"/>
-      <c r="AK1" s="42"/>
-      <c r="AL1" s="42"/>
-      <c r="AM1" s="42"/>
-      <c r="AN1" s="42"/>
-      <c r="AO1" s="42"/>
-      <c r="AP1" s="42"/>
-      <c r="AQ1" s="42"/>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="42"/>
-      <c r="AT1" s="42"/>
-      <c r="AU1" s="42"/>
-      <c r="AV1" s="42"/>
-      <c r="AW1" s="42"/>
-      <c r="AX1" s="42"/>
-      <c r="AY1" s="42"/>
-      <c r="AZ1" s="42"/>
-      <c r="BA1" s="42"/>
-      <c r="BB1" s="42"/>
-      <c r="BC1" s="42"/>
-      <c r="BD1" s="42"/>
-      <c r="BE1" s="42"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="55"/>
+      <c r="AC1" s="55"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="55"/>
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="55"/>
+      <c r="AR1" s="55"/>
+      <c r="AS1" s="55"/>
+      <c r="AT1" s="55"/>
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="55"/>
+      <c r="BB1" s="55"/>
+      <c r="BC1" s="55"/>
+      <c r="BD1" s="55"/>
+      <c r="BE1" s="55"/>
     </row>
     <row r="2" customFormat="1" ht="39.75" customHeight="1" spans="1:57">
       <c r="A2" s="9"/>
@@ -2891,97 +3120,97 @@
       <c r="F2" s="11"/>
       <c r="G2" s="17"/>
       <c r="H2" s="18"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="31" t="s">
+      <c r="I2" s="40"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="35">
+      <c r="K2" s="41">
         <f>SUMIF(H:H,"F",D:D)</f>
-        <v>1245000</v>
-      </c>
-      <c r="L2" s="35">
+        <v>1565742</v>
+      </c>
+      <c r="L2" s="41">
         <f>SUMIF(H:H,"B",D:D)</f>
-        <v>614793</v>
-      </c>
-      <c r="M2" s="35">
+        <v>252500</v>
+      </c>
+      <c r="M2" s="41">
         <f>SUMIF(H:H,"K",D:D)</f>
-        <v>1512836</v>
-      </c>
-      <c r="N2" s="35">
+        <v>1985977</v>
+      </c>
+      <c r="N2" s="41">
         <f>SUMIF(H:H,"S",D:D)</f>
         <v>0</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="41">
         <f>SUMIF(H:H,"M",D:D)-SUMIF(H:H,"M",C:C)</f>
         <v>0</v>
       </c>
-      <c r="P2" s="35">
+      <c r="P2" s="41">
         <f>SUMIF(H:H,"T",C:C)-SUMIF(H:H,"T",D:D)</f>
-        <v>3062800</v>
-      </c>
-      <c r="Q2" s="35">
+        <v>3011400</v>
+      </c>
+      <c r="Q2" s="41">
         <f>SUMIF(H:H,"I",C:C)</f>
-        <v>4844</v>
-      </c>
-      <c r="R2" s="35">
-        <f>(P2+Q2)-O2-N2-M2-L2-K2+S2</f>
-        <v>2015</v>
-      </c>
-      <c r="S2" s="43">
+        <v>0</v>
+      </c>
+      <c r="R2" s="41">
+        <f>(E3-C3+D3)+(SUM(C:C)-SUM(D:D))</f>
+        <v>12123</v>
+      </c>
+      <c r="S2" s="52">
         <v>307000</v>
       </c>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="42"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
-      <c r="AM2" s="42"/>
-      <c r="AN2" s="42"/>
-      <c r="AO2" s="42"/>
-      <c r="AP2" s="42"/>
-      <c r="AQ2" s="42"/>
-      <c r="AR2" s="42"/>
-      <c r="AS2" s="42"/>
-      <c r="AT2" s="42"/>
-      <c r="AU2" s="42"/>
-      <c r="AV2" s="42"/>
-      <c r="AW2" s="42"/>
-      <c r="AX2" s="42"/>
-      <c r="AY2" s="42"/>
-      <c r="AZ2" s="42"/>
-      <c r="BA2" s="42"/>
-      <c r="BB2" s="42"/>
-      <c r="BC2" s="42"/>
-      <c r="BD2" s="42"/>
-      <c r="BE2" s="42"/>
-    </row>
-    <row r="3" customFormat="1" ht="233.1" customHeight="1" spans="1:19">
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
+      <c r="BC2" s="55"/>
+      <c r="BD2" s="55"/>
+      <c r="BE2" s="55"/>
+    </row>
+    <row r="3" customFormat="1" ht="110.9" customHeight="1" spans="1:20">
       <c r="A3" s="12">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14">
-        <v>299400</v>
+        <v>155247</v>
       </c>
       <c r="E3" s="19">
-        <v>7600</v>
+        <v>649695</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>21</v>
@@ -2990,6 +3219,7 @@
       <c r="H3" s="22" t="s">
         <v>22</v>
       </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -2999,29 +3229,31 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="3"/>
-    </row>
-    <row r="4" customFormat="1" ht="80" customHeight="1" spans="1:19">
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" customFormat="1" ht="111.2" customHeight="1" spans="1:20">
       <c r="A4" s="12">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="14">
-        <v>3000000</v>
-      </c>
-      <c r="D4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14">
+        <v>100180</v>
+      </c>
       <c r="E4" s="19">
-        <f t="shared" ref="E4:E31" si="0">E3+C4-D4</f>
-        <v>3007600</v>
-      </c>
-      <c r="F4" s="23" t="s">
+        <f t="shared" ref="E4:E23" si="0">E3+C4-D4</f>
+        <v>549515</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="24"/>
+      <c r="G4" s="21"/>
       <c r="H4" s="22" t="s">
-        <v>25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -3031,29 +3263,31 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="3"/>
-    </row>
-    <row r="5" customFormat="1" ht="80" customHeight="1" spans="1:19">
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" customFormat="1" ht="101.4" customHeight="1" spans="1:20">
       <c r="A5" s="12">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14">
-        <v>1200</v>
+        <v>200000</v>
       </c>
       <c r="E5" s="19">
         <f t="shared" si="0"/>
-        <v>3006400</v>
+        <v>349515</v>
       </c>
       <c r="F5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="22" t="s">
-        <v>25</v>
-      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -3063,10 +3297,11 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="3"/>
-    </row>
-    <row r="6" customFormat="1" ht="111.4" customHeight="1" spans="1:19">
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" customFormat="1" ht="115.4" customHeight="1" spans="1:20">
       <c r="A6" s="12">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>28</v>
@@ -3077,7 +3312,7 @@
       </c>
       <c r="E6" s="19">
         <f t="shared" si="0"/>
-        <v>2658900</v>
+        <v>2015</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>29</v>
@@ -3086,6 +3321,7 @@
       <c r="H6" s="22" t="s">
         <v>22</v>
       </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -3095,29 +3331,31 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="3"/>
-    </row>
-    <row r="7" customFormat="1" ht="241.5" customHeight="1" spans="1:19">
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" customFormat="1" ht="80" customHeight="1" spans="1:20">
       <c r="A7" s="12">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14">
-        <v>88200</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C7" s="14">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="14"/>
       <c r="E7" s="19">
         <f t="shared" si="0"/>
-        <v>2570700</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="21"/>
+        <v>3002015</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="25"/>
       <c r="H7" s="22" t="s">
-        <v>31</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -3127,29 +3365,31 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="3"/>
-    </row>
-    <row r="8" customFormat="1" ht="115.65" customHeight="1" spans="1:19">
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" customFormat="1" ht="80" customHeight="1" spans="1:20">
       <c r="A8" s="12">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14">
-        <v>157500</v>
+        <v>1200</v>
       </c>
       <c r="E8" s="19">
         <f t="shared" si="0"/>
-        <v>2413200</v>
+        <v>3000815</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="21"/>
+        <v>34</v>
+      </c>
+      <c r="G8" s="27"/>
       <c r="H8" s="22" t="s">
-        <v>31</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -3159,29 +3399,31 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="3"/>
-    </row>
-    <row r="9" customFormat="1" ht="409.5" customHeight="1" spans="1:19">
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" customFormat="1" ht="388.15" customHeight="1" spans="1:20">
       <c r="A9" s="12">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14">
-        <v>21500</v>
+        <v>605000</v>
       </c>
       <c r="E9" s="19">
         <f t="shared" si="0"/>
-        <v>2391700</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="21"/>
+        <v>2395815</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="29"/>
       <c r="H9" s="22" t="s">
-        <v>31</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -3191,29 +3433,31 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="3"/>
-    </row>
-    <row r="10" customFormat="1" ht="212.45" customHeight="1" spans="1:19">
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" customFormat="1" ht="127.35" customHeight="1" spans="1:20">
       <c r="A10" s="12">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14">
-        <v>68000</v>
+        <v>381970</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" si="0"/>
-        <v>2323700</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>37</v>
+        <v>2013845</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>38</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="22" t="s">
-        <v>38</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -3223,29 +3467,31 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="3"/>
-    </row>
-    <row r="11" customFormat="1" ht="271.8" customHeight="1" spans="1:19">
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" customFormat="1" ht="248.1" customHeight="1" spans="1:20">
       <c r="A11" s="12">
-        <v>46045</v>
+        <v>46053</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14">
-        <v>46000</v>
+        <v>40000</v>
       </c>
       <c r="E11" s="19">
         <f t="shared" si="0"/>
-        <v>2277700</v>
-      </c>
-      <c r="F11" s="26" t="s">
+        <v>1973845</v>
+      </c>
+      <c r="F11" s="28" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="22" t="s">
-        <v>31</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J11" s="3"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -3255,29 +3501,31 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" customFormat="1" ht="334.35" customHeight="1" spans="1:19">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" customFormat="1" ht="213.9" customHeight="1" spans="1:20">
       <c r="A12" s="12">
-        <v>46046</v>
+        <v>46053</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14">
-        <v>65509</v>
+        <v>70000</v>
       </c>
       <c r="E12" s="19">
         <f t="shared" si="0"/>
-        <v>2212191</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>41</v>
+        <v>1903845</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>42</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="22" t="s">
-        <v>22</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -3287,31 +3535,33 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="3"/>
-    </row>
-    <row r="13" customFormat="1" ht="253" customHeight="1" spans="1:19">
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
       <c r="A13" s="12">
-        <v>46046</v>
+        <v>46053</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14">
-        <v>92500</v>
+        <v>64000</v>
       </c>
       <c r="E13" s="19">
         <f t="shared" si="0"/>
-        <v>2119691</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>43</v>
+        <v>1839845</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>44</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="22" t="s">
-        <v>38</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="36"/>
+      <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="5"/>
       <c r="O13" s="3"/>
@@ -3319,125 +3569,170 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="3"/>
-    </row>
-    <row r="14" customFormat="1" ht="237" customHeight="1" spans="1:19">
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" customFormat="1" ht="190.45" customHeight="1" spans="1:20">
       <c r="A14" s="12">
-        <v>46047</v>
+        <v>46053</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14">
-        <v>103593</v>
+        <v>87000</v>
       </c>
       <c r="E14" s="19">
         <f t="shared" si="0"/>
-        <v>2016098</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>44</v>
+        <v>1752845</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>45</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" customFormat="1" ht="381.1" customHeight="1" spans="1:19">
+        <v>22</v>
+      </c>
+      <c r="I14" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="44">
+        <f>SUMIFS(D:D,H:H,"F",A:A,S14,A:A,T14)</f>
+        <v>915000</v>
+      </c>
+      <c r="L14" s="44">
+        <f>SUMIFS(D:D,H:H,"B",A:A,S14,A:A,T14)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="44">
+        <f>SUMIFS(D:D,H:H,"K",A:A,S14,A:A,T14)</f>
+        <v>1071897</v>
+      </c>
+      <c r="N14" s="52">
+        <f>SUMIFS(D:D,H:H,"S",A:A,S14,A:A,T14)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="52">
+        <f>SUMIFS(D:D,H:H,"M",A:A,S14,A:A,T14)-SUMIFS(C:C,H:H,"M",A:A,S14,A:A,T14)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="52">
+        <f>SUMIFS(C:C,H:H,"T",A:A,S14,A:A,T14)-SUMIFS(D:D,H:H,"T",A:A,S14,A:A,T14)</f>
+        <v>2934800</v>
+      </c>
+      <c r="Q14" s="52">
+        <f>SUMIFS(C:C,H:H,"I",A:A,S14,A:A,T14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="S14" s="22" t="str">
+        <f>"&gt;="&amp;DATE(2026,1,1)</f>
+        <v>&gt;=46023</v>
+      </c>
+      <c r="T14" s="56" t="str">
+        <f>"&lt;="&amp;DATE(2026,1,31)</f>
+        <v>&lt;=46053</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="274.4" customHeight="1" spans="1:22">
       <c r="A15" s="12">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14">
-        <v>50000</v>
+        <v>20142</v>
       </c>
       <c r="E15" s="19">
         <f t="shared" si="0"/>
-        <v>1966098</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>46</v>
+        <v>1732703</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>49</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="22" t="s">
-        <v>38</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J15" s="45"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="5"/>
-      <c r="O15" s="3"/>
+      <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="3"/>
-    </row>
-    <row r="16" customFormat="1" ht="402.65" customHeight="1" spans="1:19">
+      <c r="T15"/>
+      <c r="U15" s="59"/>
+      <c r="V15" s="59"/>
+    </row>
+    <row r="16" customFormat="1" ht="108.5" customHeight="1" spans="1:20">
       <c r="A16" s="12">
-        <v>46047</v>
+        <v>46055</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14">
-        <v>73500</v>
+        <v>102500</v>
       </c>
       <c r="E16" s="19">
         <f t="shared" si="0"/>
-        <v>1892598</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>47</v>
+        <v>1630203</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>50</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="3"/>
-    </row>
-    <row r="17" customFormat="1" ht="272.35" customHeight="1" spans="1:19">
+      <c r="I16" s="42"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="58"/>
+    </row>
+    <row r="17" customFormat="1" ht="111.35" customHeight="1" spans="1:20">
       <c r="A17" s="12">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14">
-        <v>290000</v>
+        <v>149020</v>
       </c>
       <c r="E17" s="19">
         <f t="shared" si="0"/>
-        <v>1602598</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>49</v>
+        <v>1481183</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>51</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="22" t="s">
-        <v>38</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J17" s="3"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -3447,29 +3742,31 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="3"/>
-    </row>
-    <row r="18" customFormat="1" ht="208.45" customHeight="1" spans="1:19">
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" customFormat="1" ht="287.75" customHeight="1" spans="1:20">
       <c r="A18" s="12">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14">
-        <v>28000</v>
+        <v>76600</v>
       </c>
       <c r="E18" s="19">
         <f t="shared" si="0"/>
-        <v>1574598</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>51</v>
+        <v>1404583</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>53</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="22" t="s">
-        <v>31</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J18" s="3"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -3479,29 +3776,31 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="3"/>
-    </row>
-    <row r="19" customFormat="1" ht="216.9" customHeight="1" spans="1:19">
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" customFormat="1" ht="100.95" customHeight="1" spans="1:20">
       <c r="A19" s="12">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14">
-        <v>170000</v>
+        <v>149020</v>
       </c>
       <c r="E19" s="19">
         <f t="shared" si="0"/>
-        <v>1404598</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>53</v>
+        <v>1255563</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="22" t="s">
-        <v>31</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J19" s="3"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -3511,29 +3810,31 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" customFormat="1" ht="277.75" customHeight="1" spans="1:19">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" customFormat="1" ht="319.5" customHeight="1" spans="1:20">
       <c r="A20" s="12">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14">
-        <v>124000</v>
+        <v>48000</v>
       </c>
       <c r="E20" s="19">
         <f t="shared" si="0"/>
-        <v>1280598</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>55</v>
+        <v>1207563</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>56</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="22" t="s">
         <v>22</v>
       </c>
+      <c r="J20" s="3"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -3543,29 +3844,31 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="3"/>
-    </row>
-    <row r="21" customFormat="1" ht="378.6" customHeight="1" spans="1:19">
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" customFormat="1" ht="229.55" customHeight="1" spans="1:20">
       <c r="A21" s="12">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14">
-        <v>544500</v>
+        <v>108000</v>
       </c>
       <c r="E21" s="19">
         <f t="shared" si="0"/>
-        <v>736098</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>57</v>
+        <v>1099563</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>58</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="22" t="s">
-        <v>38</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J21" s="3"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -3575,29 +3878,31 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="3"/>
-    </row>
-    <row r="22" customFormat="1" ht="398.8" customHeight="1" spans="1:18">
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" customFormat="1" ht="260.1" customHeight="1" spans="1:20">
       <c r="A22" s="12">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="14">
-        <v>64000</v>
-      </c>
-      <c r="D22" s="14"/>
+        <v>59</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14">
+        <v>263000</v>
+      </c>
       <c r="E22" s="19">
         <f t="shared" si="0"/>
-        <v>800098</v>
+        <v>836563</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="22" t="s">
-        <v>25</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J22" s="3"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -3606,60 +3911,67 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-    </row>
-    <row r="23" customFormat="1" ht="110.9" customHeight="1" spans="1:18">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" customFormat="1" ht="233.15" customHeight="1" spans="1:20">
       <c r="A23" s="12">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14">
-        <v>155247</v>
+        <v>252500</v>
       </c>
       <c r="E23" s="19">
         <f t="shared" si="0"/>
-        <v>644851</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>61</v>
+        <v>584063</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>62</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-    </row>
-    <row r="24" customFormat="1" ht="111.2" customHeight="1" spans="1:18">
+        <v>63</v>
+      </c>
+      <c r="I23" s="42"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="58"/>
+    </row>
+    <row r="24" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
       <c r="A24" s="12">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14">
-        <v>100180</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C24" s="14">
+        <v>76600</v>
+      </c>
+      <c r="D24" s="14"/>
       <c r="E24" s="19">
-        <f t="shared" si="0"/>
-        <v>544671</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>63</v>
+        <f t="shared" ref="E24:E60" si="1">E23+C24-D24</f>
+        <v>660663</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>64</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="22" t="s">
-        <v>22</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J24" s="3"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -3668,29 +3980,32 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-    </row>
-    <row r="25" customFormat="1" ht="101.4" customHeight="1" spans="1:18">
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" customFormat="1" ht="244.85" customHeight="1" spans="1:20">
       <c r="A25" s="12">
-        <v>46050</v>
+        <v>46060</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14">
-        <v>200000</v>
+        <v>58000</v>
       </c>
       <c r="E25" s="19">
-        <f t="shared" si="0"/>
-        <v>344671</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>65</v>
+        <f t="shared" si="1"/>
+        <v>602663</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>66</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="22" t="s">
-        <v>38</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J25" s="3"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -3699,29 +4014,32 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
-    </row>
-    <row r="26" customFormat="1" ht="115.4" customHeight="1" spans="1:18">
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" customFormat="1" ht="263.5" customHeight="1" spans="1:20">
       <c r="A26" s="12">
-        <v>46050</v>
+        <v>46060</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14">
-        <v>347500</v>
+        <v>12500</v>
       </c>
       <c r="E26" s="19">
-        <f t="shared" si="0"/>
-        <v>-2829</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>66</v>
+        <f t="shared" si="1"/>
+        <v>590163</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>68</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="22" t="s">
-        <v>22</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J26" s="3"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -3730,71 +4048,102 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-    </row>
-    <row r="27" customFormat="1" ht="289.3" customHeight="1" spans="1:18">
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" customFormat="1" ht="238.85" customHeight="1" spans="1:20">
       <c r="A27" s="12">
-        <v>46050</v>
+        <v>46060</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="14">
-        <v>4844</v>
-      </c>
-      <c r="D27" s="14"/>
+        <v>69</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14">
+        <v>42500</v>
+      </c>
       <c r="E27" s="19">
-        <f t="shared" si="0"/>
-        <v>2015</v>
+        <f t="shared" si="1"/>
+        <v>547663</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-    </row>
-    <row r="28" customFormat="1" ht="15.75" customHeight="1" spans="1:18">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="I27" s="47"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="58"/>
+    </row>
+    <row r="28" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
+      <c r="A28" s="12">
+        <v>46061</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+      <c r="D28" s="14">
+        <v>167500</v>
+      </c>
       <c r="E28" s="19">
-        <f t="shared" si="0"/>
-        <v>2015</v>
-      </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="22"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-    </row>
-    <row r="29" customFormat="1" ht="15.75" customHeight="1" spans="1:18">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
+        <f t="shared" si="1"/>
+        <v>380163</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="47"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="58"/>
+    </row>
+    <row r="29" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
+      <c r="A29" s="12">
+        <v>46063</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+      <c r="D29" s="14">
+        <v>149020</v>
+      </c>
       <c r="E29" s="19">
-        <f t="shared" si="0"/>
-        <v>2015</v>
-      </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="22"/>
+        <f t="shared" si="1"/>
+        <v>231143</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="3"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -3803,19 +4152,32 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
-    </row>
-    <row r="30" customFormat="1" ht="15.75" customHeight="1" spans="1:18">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" customFormat="1" ht="112" customHeight="1" spans="1:20">
+      <c r="A30" s="12">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="D30" s="14">
+        <v>149020</v>
+      </c>
       <c r="E30" s="19">
-        <f t="shared" si="0"/>
-        <v>2015</v>
-      </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="22"/>
+        <f t="shared" si="1"/>
+        <v>82123</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="3"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -3824,19 +4186,32 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
-    </row>
-    <row r="31" customFormat="1" ht="15.75" customHeight="1" spans="1:18">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" customFormat="1" ht="203.65" customHeight="1" spans="1:20">
+      <c r="A31" s="12">
+        <v>46063</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>41</v>
+      </c>
       <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="D31" s="14">
+        <v>70000</v>
+      </c>
       <c r="E31" s="19">
-        <f t="shared" si="0"/>
-        <v>2015</v>
-      </c>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="22"/>
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="3"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -3845,36 +4220,739 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F32" s="31"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="22"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+    </row>
+    <row r="33" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="22"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F34" s="31"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="22"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F35" s="31"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="22"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+    </row>
+    <row r="36" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F36" s="31"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="22"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+    </row>
+    <row r="37" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F37" s="31"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="22"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+    </row>
+    <row r="38" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F38" s="31"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="22"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+    </row>
+    <row r="39" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F39" s="31"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="22"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F40" s="31"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="22"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F41" s="31"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="22"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+    </row>
+    <row r="42" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F42" s="31"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="22"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+    </row>
+    <row r="43" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F43" s="31"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="22"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+    </row>
+    <row r="44" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F44" s="31"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="22"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+    </row>
+    <row r="45" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F45" s="31"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="22"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F46" s="31"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="22"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+    </row>
+    <row r="47" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F47" s="31"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="22"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+    </row>
+    <row r="48" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F48" s="31"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="22"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+    </row>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F49" s="31"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="22"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+    </row>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F50" s="31"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="22"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+    </row>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F51" s="31"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="22"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+    </row>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F52" s="31"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="22"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+    </row>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F53" s="31"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="22"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F54" s="31"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="22"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+    </row>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F55" s="31"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="22"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F56" s="31"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="22"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F57" s="31"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="22"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+    </row>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F58" s="31"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="22"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+    </row>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F59" s="31"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="22"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" customFormat="1" ht="51.2" spans="1:20">
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="19">
+        <f t="shared" si="1"/>
+        <v>12123</v>
+      </c>
+      <c r="F60" s="35"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="K60" s="44">
+        <f>SUMIFS(D:D,H:H,"F",A:A,S60,A:A,T60)</f>
+        <v>650742</v>
+      </c>
+      <c r="L60" s="44">
+        <f>SUMIFS(D:D,H:H,"B",A:A,S60,A:A,T60)</f>
+        <v>252500</v>
+      </c>
+      <c r="M60" s="44">
+        <f>SUMIFS(D:D,H:H,"K",A:A,S60,A:A,T60)</f>
+        <v>914080</v>
+      </c>
+      <c r="N60" s="52">
+        <f>SUMIFS(D:D,H:H,"S",A:A,S60,A:A,T60)</f>
+        <v>0</v>
+      </c>
+      <c r="O60" s="52">
+        <f>SUMIFS(D:D,H:H,"M",A:A,S60,A:A,T60)-SUMIFS(C:C,H:H,"M",A:A,S60,A:A,T60)</f>
+        <v>0</v>
+      </c>
+      <c r="P60" s="52">
+        <f>SUMIFS(C:C,H:H,"T",A:A,S60,A:A,T60)-SUMIFS(D:D,H:H,"T",A:A,S60,A:A,T60)</f>
+        <v>76600</v>
+      </c>
+      <c r="Q60" s="52">
+        <f>SUMIFS(C:C,H:H,"I",A:A,S60,A:A,T60)</f>
+        <v>0</v>
+      </c>
+      <c r="R60" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="S60" s="22" t="str">
+        <f>"&gt;="&amp;DATE(2026,2,1)</f>
+        <v>&gt;=46054</v>
+      </c>
+      <c r="T60" s="56" t="str">
+        <f>"&lt;="&amp;DATE(2026,2,31)</f>
+        <v>&lt;=46084</v>
+      </c>
+    </row>
     <row r="61" ht="15.75" customHeight="1"/>
     <row r="62" ht="15.75" customHeight="1"/>
     <row r="63" ht="15.75" customHeight="1"/>
@@ -4627,31 +5705,6 @@
     <row r="810" ht="15.75" customHeight="1"/>
     <row r="811" ht="15.75" customHeight="1"/>
     <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:A2"/>
@@ -4661,7 +5714,7 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G7:G8"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
   </mergeCells>

--- a/Petty cash for proposal.xlsx
+++ b/Petty cash for proposal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16000" windowHeight="17020" firstSheet="2"/>
+    <workbookView windowWidth="16020" windowHeight="17020" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Petty Cash Andika" sheetId="34" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="63">
   <si>
     <t>Tanggal</t>
   </si>
@@ -89,179 +89,140 @@
     <t>DEPT. TOTAL :</t>
   </si>
   <si>
-    <t>KEMFOOD BALI</t>
-  </si>
-  <si>
-    <t>PURCHASE SALAMI 1 KG</t>
+    <t>BANK BRI</t>
+  </si>
+  <si>
+    <t>TOPPED UP RP. 3.000.000</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>OVO</t>
+  </si>
+  <si>
+    <t>ADMIN FEE RP. 1.200</t>
+  </si>
+  <si>
+    <t>TRANSFER KE LADANG ROTI KREATIF PT</t>
+  </si>
+  <si>
+    <t>PAYMENT FOR PURCHASE OF 20 PCS OF BRIOCHE BUN FROM BRAUD</t>
   </si>
   <si>
     <t>K</t>
   </si>
   <si>
+    <t>PAYMENT FOR PURCHASE OF 10 PCS OF PLAIN CROISSANT FROM BRAUD</t>
+  </si>
+  <si>
+    <t>TRANSFER KE KADEK ANDIKA PUTRA</t>
+  </si>
+  <si>
+    <t>REIMBURSE PURCHASE OF WATER FILTER REFILL FOR EMERGENCY TO ANDIKA PURCHASING FOR TRANSACTION DATED 10TH FEB 2026</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>REIMBURSE PRINTIS OF BAR INVENTORY AND RECIPEE USING TO ANDIKA PURCHASING FOR TRANSACTION DATED 11TH FEB 2026</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>TRANSFER KE OLMEC INDUSTRIES INDONESIA PT</t>
   </si>
   <si>
-    <t>PURCHASE NACHOS 2 PAX</t>
-  </si>
-  <si>
-    <t>KIMMY LISTRIK</t>
-  </si>
-  <si>
-    <t>PURCHASE TRAVO FOR BAR LED LIGHTS</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>TRANSFER KE LADANG ROTI KREATIF PT</t>
-  </si>
-  <si>
-    <t>PAYMENT TO BRAUD FOR BREAD ORDER</t>
-  </si>
-  <si>
-    <t>BANK BRI</t>
-  </si>
-  <si>
-    <t>TOPPED UP RP. 3.000.000</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>OVO ADMIN FEE</t>
-  </si>
-  <si>
-    <t>ADMIN FEE RP. 1.200</t>
-  </si>
-  <si>
-    <t>TRANSFER KE KADEK ANDIKA PUTRA</t>
-  </si>
-  <si>
-    <t>REIMBURSE DOWNPAYMENT OF HADYMAN FOR BAR CEILLING WORK TO ANDIKA PURCHASING</t>
+    <t>PURCHASE 1 KG OF NACHOS AND 6 PAX OF TORTILLA</t>
+  </si>
+  <si>
+    <t>TRANSFER KE BALI STARS CV</t>
+  </si>
+  <si>
+    <t>PRINT FLOOR STICKERS AND FLOOR JOB DESK ON SHIFT</t>
+  </si>
+  <si>
+    <t>TOKO KARYA NIRMALA</t>
+  </si>
+  <si>
+    <t>PURCHASE 3 PAINT COLOR SAMPLE FOR BAR CEILLING 1 KG EACH</t>
+  </si>
+  <si>
+    <t>REIMBURSE CHAI CHITAI GOJEK TEAS DELIVERY USING ANDIKA PURHASING PERSONAL CASH TO CASHIER AND REIMBURSED BY OVO</t>
+  </si>
+  <si>
+    <t>TRANSFER KE PT PACHIRA AQUATICA GROUP</t>
+  </si>
+  <si>
+    <t>PAYMENT TO REST OF 10% OF THE PAYMENT OF CHERRY KISS DUMPLINGS INVOICE #38</t>
+  </si>
+  <si>
+    <t>TRUE LOVE FLOWERS</t>
+  </si>
+  <si>
+    <t>PURCHASE FLOWERS FOR FLOOR</t>
+  </si>
+  <si>
+    <t>PURCHASE SAMPLE PAINT JADE JAZZ SPOTLESS 1 KG AND THINNER TO FIX ART BRUSHES</t>
+  </si>
+  <si>
+    <t>TOKOPEDIA</t>
+  </si>
+  <si>
+    <t>PURCHASE DIGITAL SCALE ON TOKOPEDIA FOR BAR</t>
+  </si>
+  <si>
+    <t>TRANSFER KE SDRI CINDY FITRIA CAHYANI</t>
+  </si>
+  <si>
+    <t>REIMBURSE PRINTOUT OF FLOOR EVALUATION FORM TO CINDY FLOOR</t>
+  </si>
+  <si>
+    <t>TRANSFER KE RIKI</t>
+  </si>
+  <si>
+    <t>REIMBURSE PURCHASE OF DOUBLE TAPE TO RIKI FLOOR</t>
+  </si>
+  <si>
+    <t>TRANSFER KE LUH DINA ANGGRA WAHY</t>
+  </si>
+  <si>
+    <t>REIMBURSE PURCHASE OF BALINESE OFFERING TO DINA FLOOR</t>
   </si>
   <si>
     <t>TRANSFER KE DINETA JAYA PT</t>
   </si>
   <si>
-    <t>PAYMENT FOR 3 PCS OF 1 KG OF SOUR CREAM TO DINETA JAYA</t>
-  </si>
-  <si>
-    <t>DEWATA INDAH</t>
-  </si>
-  <si>
-    <t>PURCHASE 4 PCS OF PLANTS</t>
-  </si>
-  <si>
-    <t>ANNA FLORIST, JLNRAYA ULU</t>
-  </si>
-  <si>
-    <t>PURCHASE FLOWERS FOR FLOOR</t>
-  </si>
-  <si>
-    <t>CM ULUWATU</t>
-  </si>
-  <si>
-    <t>REPAYMENT ACTION FOR STUCKED TRANSACTIONS REFERRING TO 11TH OF JANUARY 2026 PENDING PAYMENT TRANSACTION TO PURCHASE HAIRNET AND MASKER FOR HACCP INSPECTIONS TO CLAIM MY PERSONAL COLLATERAL CASH MONEY.</t>
-  </si>
-  <si>
-    <t>PURCHASE 3 PCS OF KEBAB STICKS</t>
-  </si>
-  <si>
-    <t>JANUARY</t>
+    <t>PAYMENT TO PURCHASE 1 PCS POLYMORPH NAPKIN TO DINETA JAYA</t>
+  </si>
+  <si>
+    <t>PAYMENT TO PURCHASE 3 PCS OF TATUA SOUR CREAM TO DINETA JAYA</t>
+  </si>
+  <si>
+    <t>GRAB</t>
+  </si>
+  <si>
+    <t>GRAB DELIVERY TO SEND 30L OF ABISEKA FRESH MILK</t>
+  </si>
+  <si>
+    <t>TRANSFER KE I PUTU SANCITHA</t>
+  </si>
+  <si>
+    <t>PURCHASE 2 PCS OF LED BULB FOR KITCHEN EXHAUST</t>
+  </si>
+  <si>
+    <t>FEBRUARY</t>
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>JIMBARAN BARU ULUWATU</t>
-  </si>
-  <si>
-    <t>PURCHASE DOOR HINGE</t>
-  </si>
-  <si>
-    <t>PAYMENT OF 2 PCS OF NAPKIN ROLL</t>
-  </si>
-  <si>
-    <t>PURCHASE 4 PCS TORTILLA WRAP AT EL TORTILLA</t>
-  </si>
-  <si>
-    <t>TOKOPEDIA</t>
-  </si>
-  <si>
-    <t>PURCHASE DEXTONE EPOXY GLUE 48 GR</t>
-  </si>
-  <si>
-    <t>PURCHASE 4 PACKS OF TORTILLA WRAP AT EL TORTILLA</t>
-  </si>
-  <si>
-    <t>MR.D.I.Y RK JIMBARAN</t>
-  </si>
-  <si>
-    <t>PURCHASE 3 PACKS OF  WHITE BOARD MARKER</t>
-  </si>
-  <si>
-    <t>ARTHAYASA PHOTO HO</t>
-  </si>
-  <si>
-    <t>PURCHASE 1 BOX OF STAPLES REFILL FOR FLOOR</t>
-  </si>
-  <si>
-    <t>SURYA JAYA ELEKTRIK HO</t>
-  </si>
-  <si>
-    <t>PURCHASE CUSTOM MADE ELECTRICAL SOCKET 15 METER CABLE LENGTH</t>
-  </si>
-  <si>
-    <t>TRANSFER KE NI LUH MULIA DEWI</t>
-  </si>
-  <si>
-    <t>PAYMENT TO MULIA JAYA FOR PASSION FRUIT</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>REFUND TOKOPEDIA CANCELLED TRANSACTIONS BY SELLER (REFERENCE: 6 FEB 2026 PURCHASE DEXTONE EPOXY GLUE 48 GR)</t>
-  </si>
-  <si>
-    <t>MITRA 10 GATSU, BALI</t>
-  </si>
-  <si>
-    <t>PURCHASE 4 PCS OF DEXTONE EPOXY GLUE 48 GR TO FIX RESTAURANT TABLE</t>
-  </si>
-  <si>
-    <t>TRANSFER KE I WAYAN GEDE SUDIARTHA S</t>
-  </si>
-  <si>
-    <t>PURCHASE OF NAILS TO FIX KITCHEN DOOR</t>
-  </si>
-  <si>
-    <t>TRANSFER KE LUH DINA ANGGRA WAHY</t>
-  </si>
-  <si>
-    <t>REIMBURSE FLOOR BALINESE OFFERING TO DINA FLOOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAYMENT FOR BRAUD BREAD </t>
-  </si>
-  <si>
-    <t>1ST ATTEMPT ON PURCHASE OF TORTILLA FAILED AND RESULTING IN PENDING PAYMENT.</t>
-  </si>
-  <si>
-    <t>PURCHASE OF TORTILLA</t>
-  </si>
-  <si>
-    <t>PURCHASE FLOOR FLOWER</t>
-  </si>
-  <si>
-    <t>FEBRUARY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -270,7 +231,6 @@
     <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@"/>
     <numFmt numFmtId="182" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="183" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="184" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -484,7 +444,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,6 +461,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF99CCFF"/>
         <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -530,6 +496,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -643,12 +615,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -714,7 +680,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -906,19 +872,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
@@ -1052,7 +1005,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1064,119 +1017,119 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1213,7 +1166,7 @@
     <xf numFmtId="182" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1234,10 +1187,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -1246,39 +1199,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="182" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1291,40 +1232,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1333,10 +1268,19 @@
     <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1345,16 +1289,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1643,34 +1581,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>35877</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>24447</xdr:rowOff>
+      <xdr:colOff>36830</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>26035</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2189797</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1386522</xdr:rowOff>
+      <xdr:colOff>2186305</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>932815</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="ID_F0AC9804840F4BB9BB272032208A820C" descr="PHOTO-2026-01-28-10-32-20"/>
+        <xdr:cNvPr id="60" name="ID_117AF324B2E54403A0027958D97597D3" descr="PHOTO-2026-02-17-23-16-57"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
-        <a:srcRect t="7965" b="5200"/>
+        <a:srcRect t="5844" b="56620"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12368530" y="637540"/>
-          <a:ext cx="1362075" cy="2153920"/>
+        <a:xfrm>
+          <a:off x="11974195" y="1249045"/>
+          <a:ext cx="2149475" cy="1859280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1682,34 +1620,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>29527</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>24447</xdr:rowOff>
+      <xdr:colOff>38417</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25717</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2196782</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1398587</xdr:rowOff>
+      <xdr:colOff>2184717</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1276032</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="ID_F71D9C669D8C4463B4C7EEA86E536043" descr="PHOTO-2026-01-28-11-08-21"/>
+        <xdr:cNvPr id="61" name="ID_2F942794101A48C3BF74ECEE9AFD71FE" descr="PHOTO-2026-02-17-22-35-02"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect t="8832"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="12362815" y="2045335"/>
-          <a:ext cx="1374140" cy="2167255"/>
+          <a:off x="12423140" y="2705100"/>
+          <a:ext cx="1250315" cy="2146300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1721,19 +1658,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>39052</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>26035</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2186622</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1263967</xdr:rowOff>
+      <xdr:colOff>2185035</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1276350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="ID_9A15E299FC5845389941E72A5069E4F8" descr="PHOTO-2026-01-28-12-12-05"/>
+        <xdr:cNvPr id="62" name="ID_EDA91336CEC046F4B728A084FA2F716D" descr="PHOTO-2026-02-17-22-56-57"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1746,8 +1683,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="12429490" y="3399790"/>
-          <a:ext cx="1240155" cy="2147570"/>
+          <a:off x="12423775" y="4004310"/>
+          <a:ext cx="1250315" cy="2146935"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1759,76 +1696,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>33020</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>24765</xdr:rowOff>
+      <xdr:colOff>27305</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>33020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2193290</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1447800</xdr:rowOff>
+      <xdr:colOff>2202180</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>3344545</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="ID_EC0844A916624A2F93221FEB4CD1F711"/>
+        <xdr:cNvPr id="63" name="ID_C5C3DA62DE964683A31FBC51A073DD7F" descr="PHOTO-2026-02-11-16-03-32"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId4"/>
+        <a:srcRect b="32881"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11970385" y="5142865"/>
-          <a:ext cx="2160270" cy="1423035"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>35560</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2192020</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>1005840</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="ID_BCA39D04776E45DF855A9B725BB0F766" descr="PHOTO-2026-01-30-13-56-39"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect t="6129" b="53832"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11972925" y="6606540"/>
-          <a:ext cx="2156460" cy="1998980"/>
+          <a:off x="11964670" y="5757545"/>
+          <a:ext cx="2174875" cy="3311525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1840,112 +1735,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>32385</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>27305</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2197735</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>1599565</xdr:rowOff>
+      <xdr:colOff>2197100</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>4804410</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="ID_94E360EC8BCA433DB3C759F952108DD8" descr="PHOTO-2026-01-30-15-46-11"/>
+        <xdr:cNvPr id="64" name="ID_9DE52905BF4246028F84F6828B2B9C31" descr="PHOTO-2026-02-11-13-07-42"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:srcRect l="9895" t="19029" r="9927" b="5568"/>
+        <a:blip r:embed="rId5"/>
+        <a:srcRect l="12490" t="4626" r="8009"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11967845" y="13568045"/>
-          <a:ext cx="2167255" cy="1576705"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>23495</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>35560</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2204720</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>4902200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="ID_402A5938337645BC98F954A6E7617C29" descr="PHOTO-2026-01-30-13-27-45"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:srcRect t="3756" b="33327"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11960860" y="8651240"/>
-          <a:ext cx="2181225" cy="4866640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>23495</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2204720</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>3135630</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="ID_5DA81C62E9EF4E60A048CA21F1DC9AEC" descr="PHOTO-2026-01-31-10-00-42"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:srcRect b="22372"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11960860" y="15193010"/>
-          <a:ext cx="2181225" cy="3105150"/>
+          <a:off x="11969750" y="9120505"/>
+          <a:ext cx="2164715" cy="4777105"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1958,33 +1775,32 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>26670</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2201545</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>2690495</xdr:rowOff>
+      <xdr:colOff>2207895</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3328035</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="ID_5CEAC97CD50F456BAA51F453804F75F0" descr="PHOTO-2026-01-31-10-52-44"/>
+        <xdr:cNvPr id="65" name="ID_FE39A3A6CDCD48C091E3BBAC8D22C38B" descr="PHOTO-2026-02-18-01-10-32"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:srcRect t="33077"/>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11964035" y="18336260"/>
-          <a:ext cx="2174875" cy="2667635"/>
+          <a:off x="11964035" y="20387310"/>
+          <a:ext cx="2181225" cy="3303905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1996,73 +1812,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>369570</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1858010</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>5184775</xdr:rowOff>
+      <xdr:colOff>2208530</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3164205</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="ID_A1FEAEBC090D4B3BB742BD19E2FE29C4" descr="PHOTO-2026-01-31-11-09-00"/>
+        <xdr:cNvPr id="66" name="ID_2E9BA3D1A2AC44599D4692A6B3708819" descr="PHOTO-2026-02-18-15-06-41"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:srcRect t="2904" b="25044"/>
+        <a:blip r:embed="rId7"/>
+        <a:srcRect t="9460" b="12746"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12306935" y="21052790"/>
-          <a:ext cx="1488440" cy="5161915"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2202180</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>2399030</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="ID_9C36C34BF19A4EB3BC7BCB206F270E3F" descr="PHOTO-2026-01-31-11-11-45"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:srcRect t="4299" b="36109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11962765" y="26253440"/>
-          <a:ext cx="2176780" cy="2376170"/>
+          <a:off x="11963400" y="17204055"/>
+          <a:ext cx="2182495" cy="3140075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2075,33 +1852,33 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>24765</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2203450</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>3458845</xdr:rowOff>
+      <xdr:colOff>2209800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1988185</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="ID_FC1087157EAD4FE2A7963D7B42004ECE" descr="PHOTO-2026-02-01-15-14-44"/>
+        <xdr:cNvPr id="67" name="ID_3518130A34914F028D897E409584859F" descr="PHOTO-2026-02-18-12-18-22"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:srcRect b="17058"/>
+        <a:blip r:embed="rId8"/>
+        <a:srcRect t="9085" b="41047"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11962130" y="28675965"/>
-          <a:ext cx="2178685" cy="3432175"/>
+          <a:off x="11962130" y="15209520"/>
+          <a:ext cx="2185035" cy="1964055"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2113,33 +1890,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
+      <xdr:colOff>41592</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2198370</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1365250</xdr:rowOff>
+      <xdr:colOff>2192337</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1234122</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="ID_2BCA740AFE064935A5806840BB1E9367" descr="PHOTO-2026-02-02-13-42-36"/>
+        <xdr:cNvPr id="68" name="ID_B70ADF5FEC274604B67AE4FEB8E28880" descr="PHOTO-2026-02-18-10-46-28"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
+        <a:blip r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11967845" y="32157670"/>
-          <a:ext cx="2167890" cy="1341755"/>
+        <a:xfrm rot="16200000">
+          <a:off x="12448540" y="13482955"/>
+          <a:ext cx="1210310" cy="2150745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2151,34 +1928,34 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>36195</xdr:rowOff>
+      <xdr:colOff>24130</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2202815</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>2940050</xdr:rowOff>
+      <xdr:colOff>2209800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3536315</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="ID_F0A27C0ABDA846ABB27C587C95EC34D0" descr="PHOTO-2026-02-06-15-16-59"/>
+        <xdr:cNvPr id="69" name="ID_5B37C77A3F4140AF9DA2299E1EDEBF35" descr="PHOTO-2026-02-20-12-45-05"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:srcRect b="28638"/>
+        <a:blip r:embed="rId10"/>
+        <a:srcRect b="17023"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11969115" y="50175160"/>
-          <a:ext cx="2171065" cy="2903855"/>
+          <a:off x="11961495" y="28784550"/>
+          <a:ext cx="2185670" cy="3512185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2190,34 +1967,306 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>29845</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
+      <xdr:colOff>24130</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>33655</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2193290</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1400175</xdr:rowOff>
+      <xdr:colOff>2210435</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>5026660</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="ID_AD1042828E374395ACC38CF1834F1462" descr="PHOTO-2026-02-03-14-12-48"/>
+        <xdr:cNvPr id="70" name="ID_1B6332B2AE8E43E5985E9DF6A1B918BD" descr="PHOTO-2026-02-20-12-07-21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:srcRect t="4047" b="33969"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11961495" y="23748365"/>
+          <a:ext cx="2186305" cy="4993005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>26670</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2207260</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3338830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="ID_C66982ED8AA241EFBFF6CCE4CCF8196C" descr="PHOTO-2026-02-20-16-31-49"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:srcRect t="9250" b="10835"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11964035" y="32338645"/>
+          <a:ext cx="2180590" cy="3314700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2205990</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2512695</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="ID_A8891272E2D04A62BD4AB7874D2F4850" descr="PHOTO-2026-02-20-18-06-06"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:srcRect t="7524" b="44265"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11965940" y="35701605"/>
+          <a:ext cx="2177415" cy="2488565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>24130</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2210435</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>5029200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="ID_C89AE3992AE740D78413CAF51B71106C" descr="PHOTO-2026-02-20-18-13-10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:srcRect t="4047" b="33855"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11961495" y="38241605"/>
+          <a:ext cx="2186305" cy="4997450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2212340</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2916555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="ID_678587135DE747779861E02B3AF4E6FD" descr="PHOTO-2026-02-22-11-43-42"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId15"/>
-        <a:srcRect t="8031"/>
+        <a:srcRect t="8876" b="21597"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12362180" y="33143825"/>
-          <a:ext cx="1373505" cy="2163445"/>
+        <a:xfrm>
+          <a:off x="11960225" y="47490380"/>
+          <a:ext cx="2189480" cy="2892425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2212340</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>4191000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="ID_9A2284CC8EBF4C76BE520007BD6057DB" descr="PHOTO-2026-02-20-18-21-28"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11960225" y="43285410"/>
+          <a:ext cx="2189480" cy="4165600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2212340</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>5041265</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="ID_F2A158B94E594F90BC09C9625656A8F1" descr="PHOTO-2026-02-23-11-42-03"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:srcRect t="3820" b="33973"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11960225" y="55451375"/>
+          <a:ext cx="2189480" cy="5015865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2212340</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>5017770</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="ID_F3D76F275C1341CD9471C68A6BE43978" descr="PHOTO-2026-02-23-11-36-35"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:srcRect t="3692" b="34132"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11960225" y="50419635"/>
+          <a:ext cx="2189480" cy="4989195"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2230,71 +2279,33 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>26035</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>32385</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>40640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2197735</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>3620135</xdr:rowOff>
+      <xdr:colOff>2199640</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>4909185</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="ID_72F5A7BAB5AE4EB98FA06D9EB701C540" descr="PHOTO-2026-02-06-09-07-20"/>
+        <xdr:cNvPr id="78" name="ID_625EDB0EB15440C69473D927C9EABAA0" descr="PHOTO-2026-02-23-18-08-22"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:srcRect t="21456" b="6921"/>
+        <a:blip r:embed="rId19"/>
+        <a:srcRect t="5588"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11963400" y="34958655"/>
-          <a:ext cx="2171700" cy="3587750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>48577</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>25717</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2174557</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1248092</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="ID_43FFD2933CBD452EAB495FF2A9CFB257" descr="PHOTO-2026-02-06-11-36-47"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12437110" y="38153975"/>
-          <a:ext cx="1222375" cy="2125980"/>
+          <a:off x="11963400" y="60528200"/>
+          <a:ext cx="2173605" cy="4868545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2307,421 +2318,32 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>26035</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>40005</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>35560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2197735</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>4025265</xdr:rowOff>
+      <xdr:colOff>2199640</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>4250055</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="ID_63F3B46FF3854C948831037D58655375" descr="PHOTO-2026-02-06-12-45-45"/>
+        <xdr:cNvPr id="79" name="ID_D1DB5161487C43E489B231D987B2E0F4" descr="PHOTO-2026-02-23-17-01-25"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId18"/>
+        <a:blip r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11963400" y="39902765"/>
-          <a:ext cx="2171700" cy="3985260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>26035</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2197735</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2892425</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="ID_F97F2F063AF548E19B5243CED2218331" descr="PHOTO-2026-02-06-12-54-09"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId19"/>
-        <a:srcRect b="28217"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11963400" y="43953430"/>
-          <a:ext cx="2171700" cy="2859405"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>26035</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>33655</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2197735</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>3275330</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="ID_E598DCBE7B4B46E6B40DA849DD060CEF" descr="PHOTO-2026-02-06-13-20-21"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId20"/>
-        <a:srcRect l="4154" t="6903" b="15133"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11963400" y="46869350"/>
-          <a:ext cx="2171700" cy="3241675"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>23495</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2207260</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>3328670</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="ID_6545CE772D0C4FD68085584DF2013A8B" descr="PHOTO-2026-02-07-11-42-00"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId21"/>
-        <a:srcRect b="19481"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11960860" y="61436885"/>
-          <a:ext cx="2183765" cy="3302000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>26035</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2204720</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>3009265</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="ID_A014566F8AB34DC7AA4922F2DC77588C" descr="PHOTO-2026-02-07-18-29-38"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId22"/>
-        <a:srcRect b="27001"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11963400" y="64780160"/>
-          <a:ext cx="2178685" cy="2985770"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>143510</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2087245</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>5181600</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="ID_D3284D46A7454CCA91806A85F05EAA6D" descr="PHOTO-2026-02-07-01-33-21"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId23"/>
-        <a:srcRect t="5251" b="984"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12080875" y="53123465"/>
-          <a:ext cx="1943735" cy="5158105"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2205355</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>3086735</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="ID_1075E92F8AD74260B59D72F79C7ADE65" descr="PHOTO-2026-02-07-09-35-42"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId24"/>
-        <a:srcRect t="4110" b="17594"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11962765" y="58324115"/>
-          <a:ext cx="2179955" cy="3063240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>346710</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1887220</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>5188585</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_CB24E0A27A784928BCFF986663BAB11D" descr="PHOTO-2026-02-08-15-26-12"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId25"/>
-        <a:srcRect t="4009" b="3497"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12284075" y="67814190"/>
-          <a:ext cx="1540510" cy="5164455"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>30797</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>26352</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2194242</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>1408112</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_7BE29291E98642E3B1A4501AE281BC5E" descr="PHOTO-2026-02-10-09-59-11"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="12358370" y="77826235"/>
-          <a:ext cx="1381760" cy="2163445"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2174875</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>5179060</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_58CC131D1A9A46F5A8657188A51A6CD1" descr="PHOTO-2026-02-10-14-42-00"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId27"/>
-        <a:srcRect t="3630" b="31770"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11994515" y="73014205"/>
-          <a:ext cx="2117725" cy="5155565"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>24130</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>23495</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2207895</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>2573020</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_B5E07496F2BE43EEB6633AE6D770ABED" descr="PHOTO-2026-02-10-10-52-35"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId28"/>
-        <a:srcRect t="35309" b="1219"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11961495" y="79637255"/>
-          <a:ext cx="2183765" cy="2549525"/>
+          <a:off x="11963400" y="65472310"/>
+          <a:ext cx="2173605" cy="4214495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2991,7 +2613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BE812"/>
+  <dimension ref="A1:BE790"/>
   <sheetFormatPr defaultColWidth="14.5078125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -3039,77 +2661,77 @@
       <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="48" t="s">
+      <c r="M1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="N1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="S1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="55"/>
-      <c r="AF1" s="55"/>
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="55"/>
-      <c r="AR1" s="55"/>
-      <c r="AS1" s="55"/>
-      <c r="AT1" s="55"/>
-      <c r="AU1" s="55"/>
-      <c r="AV1" s="55"/>
-      <c r="AW1" s="55"/>
-      <c r="AX1" s="55"/>
-      <c r="AY1" s="55"/>
-      <c r="AZ1" s="55"/>
-      <c r="BA1" s="55"/>
-      <c r="BB1" s="55"/>
-      <c r="BC1" s="55"/>
-      <c r="BD1" s="55"/>
-      <c r="BE1" s="55"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="52"/>
+      <c r="AC1" s="52"/>
+      <c r="AD1" s="52"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="52"/>
+      <c r="BB1" s="52"/>
+      <c r="BC1" s="52"/>
+      <c r="BD1" s="52"/>
+      <c r="BE1" s="52"/>
     </row>
     <row r="2" customFormat="1" ht="39.75" customHeight="1" spans="1:57">
       <c r="A2" s="9"/>
@@ -3120,105 +2742,95 @@
       <c r="F2" s="11"/>
       <c r="G2" s="17"/>
       <c r="H2" s="18"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="37" t="s">
+      <c r="I2" s="36"/>
+      <c r="J2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="41">
+      <c r="K2" s="37">
         <f>SUMIF(H:H,"F",D:D)</f>
-        <v>1565742</v>
-      </c>
-      <c r="L2" s="41">
+        <v>831005</v>
+      </c>
+      <c r="L2" s="37">
         <f>SUMIF(H:H,"B",D:D)</f>
-        <v>252500</v>
-      </c>
-      <c r="M2" s="41">
+        <v>293120</v>
+      </c>
+      <c r="M2" s="37">
         <f>SUMIF(H:H,"K",D:D)</f>
-        <v>1985977</v>
-      </c>
-      <c r="N2" s="41">
+        <v>1289730</v>
+      </c>
+      <c r="N2" s="37">
         <f>SUMIF(H:H,"S",D:D)</f>
         <v>0</v>
       </c>
-      <c r="O2" s="41">
+      <c r="O2" s="37">
         <f>SUMIF(H:H,"M",D:D)-SUMIF(H:H,"M",C:C)</f>
         <v>0</v>
       </c>
-      <c r="P2" s="41">
+      <c r="P2" s="37">
         <f>SUMIF(H:H,"T",C:C)-SUMIF(H:H,"T",D:D)</f>
-        <v>3011400</v>
-      </c>
-      <c r="Q2" s="41">
+        <v>2998800</v>
+      </c>
+      <c r="Q2" s="37">
         <f>SUMIF(H:H,"I",C:C)</f>
         <v>0</v>
       </c>
-      <c r="R2" s="41">
-        <f>(E3-C3+D3)+(SUM(C:C)-SUM(D:D))</f>
-        <v>12123</v>
-      </c>
-      <c r="S2" s="52">
+      <c r="R2" s="37" t="e">
+        <f>(#REF!-#REF!+#REF!)+(SUM(C:C)-SUM(D:D))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S2" s="49">
         <v>307000</v>
       </c>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
-      <c r="BC2" s="55"/>
-      <c r="BD2" s="55"/>
-      <c r="BE2" s="55"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="52"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="52"/>
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="52"/>
+      <c r="AZ2" s="52"/>
+      <c r="BA2" s="52"/>
+      <c r="BB2" s="52"/>
+      <c r="BC2" s="52"/>
+      <c r="BD2" s="52"/>
+      <c r="BE2" s="52"/>
     </row>
-    <row r="3" customFormat="1" ht="110.9" customHeight="1" spans="1:20">
-      <c r="A3" s="12">
-        <v>46050</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>20</v>
-      </c>
+    <row r="3" customFormat="1" ht="16.8" spans="1:20">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="14"/>
-      <c r="D3" s="14">
-        <v>155247</v>
-      </c>
+      <c r="D3" s="14"/>
       <c r="E3" s="19">
-        <v>649695</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>21</v>
-      </c>
+        <v>54143</v>
+      </c>
+      <c r="F3" s="20"/>
       <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
-        <v>22</v>
-      </c>
+      <c r="H3" s="22"/>
       <c r="J3" s="3"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -3231,25 +2843,25 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
     </row>
-    <row r="4" customFormat="1" ht="111.2" customHeight="1" spans="1:20">
+    <row r="4" customFormat="1" ht="75" customHeight="1" spans="1:20">
       <c r="A4" s="12">
-        <v>46050</v>
+        <v>46070</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14">
-        <v>100180</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C4" s="14">
+        <v>3000000</v>
+      </c>
+      <c r="D4" s="14"/>
       <c r="E4" s="19">
-        <f t="shared" ref="E4:E23" si="0">E3+C4-D4</f>
-        <v>549515</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="21"/>
+        <f t="shared" ref="E3:E38" si="0">E3+C4-D4</f>
+        <v>3054143</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="24"/>
       <c r="H4" s="22" t="s">
         <v>22</v>
       </c>
@@ -3265,27 +2877,27 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
     </row>
-    <row r="5" customFormat="1" ht="101.4" customHeight="1" spans="1:20">
+    <row r="5" customFormat="1" ht="75" customHeight="1" spans="1:20">
       <c r="A5" s="12">
-        <v>46050</v>
+        <v>46070</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14">
-        <v>200000</v>
+        <v>1200</v>
       </c>
       <c r="E5" s="19">
         <f t="shared" si="0"/>
-        <v>349515</v>
+        <v>3052943</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="21"/>
+        <v>24</v>
+      </c>
+      <c r="G5" s="25"/>
       <c r="H5" s="22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="4"/>
@@ -3299,27 +2911,27 @@
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
     </row>
-    <row r="6" customFormat="1" ht="115.4" customHeight="1" spans="1:20">
+    <row r="6" customFormat="1" ht="102.25" customHeight="1" spans="1:20">
       <c r="A6" s="12">
-        <v>46050</v>
+        <v>46070</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14">
-        <v>347500</v>
+        <v>182500</v>
       </c>
       <c r="E6" s="19">
         <f t="shared" si="0"/>
-        <v>2015</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>29</v>
+        <v>2870443</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="22" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="4"/>
@@ -3333,27 +2945,27 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
     </row>
-    <row r="7" customFormat="1" ht="80" customHeight="1" spans="1:20">
+    <row r="7" customFormat="1" ht="102.2" customHeight="1" spans="1:20">
       <c r="A7" s="12">
-        <v>46052</v>
+        <v>46070</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="14">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="14"/>
+        <v>25</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14">
+        <v>167500</v>
+      </c>
       <c r="E7" s="19">
         <f t="shared" si="0"/>
-        <v>3002015</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="25"/>
+        <v>2702943</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="21"/>
       <c r="H7" s="22" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="4"/>
@@ -3367,32 +2979,32 @@
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
     </row>
-    <row r="8" customFormat="1" ht="80" customHeight="1" spans="1:20">
+    <row r="8" customFormat="1" ht="265.25" customHeight="1" spans="1:20">
       <c r="A8" s="12">
-        <v>46052</v>
+        <v>46070</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14">
-        <v>1200</v>
+        <v>43005</v>
       </c>
       <c r="E8" s="19">
         <f t="shared" si="0"/>
-        <v>3000815</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="27"/>
+        <v>2659938</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="21"/>
       <c r="H8" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="M8" s="46"/>
       <c r="N8" s="5"/>
       <c r="O8" s="3"/>
       <c r="P8" s="5"/>
@@ -3401,27 +3013,27 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
     </row>
-    <row r="9" customFormat="1" ht="388.15" customHeight="1" spans="1:20">
+    <row r="9" customFormat="1" ht="380.85" customHeight="1" spans="1:20">
       <c r="A9" s="12">
-        <v>46052</v>
+        <v>46070</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14">
-        <v>605000</v>
+        <v>37500</v>
       </c>
       <c r="E9" s="19">
         <f t="shared" si="0"/>
-        <v>2395815</v>
+        <v>2622438</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="29"/>
+        <v>32</v>
+      </c>
+      <c r="G9" s="21"/>
       <c r="H9" s="22" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="4"/>
@@ -3435,27 +3047,27 @@
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" customFormat="1" ht="127.35" customHeight="1" spans="1:20">
+    <row r="10" customFormat="1" ht="98.85" customHeight="1" spans="1:20">
       <c r="A10" s="12">
-        <v>46052</v>
+        <v>46071</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14">
-        <v>381970</v>
+        <v>319960</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" si="0"/>
-        <v>2013845</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>38</v>
+        <v>2302478</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="22" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="4"/>
@@ -3469,27 +3081,27 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" customFormat="1" ht="248.1" customHeight="1" spans="1:20">
+    <row r="11" customFormat="1" ht="157.05" customHeight="1" spans="1:20">
       <c r="A11" s="12">
-        <v>46053</v>
+        <v>46071</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14">
-        <v>40000</v>
+        <v>215500</v>
       </c>
       <c r="E11" s="19">
         <f t="shared" si="0"/>
-        <v>1973845</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>40</v>
+        <v>2086978</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="4"/>
@@ -3503,27 +3115,27 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
     </row>
-    <row r="12" customFormat="1" ht="213.9" customHeight="1" spans="1:20">
+    <row r="12" customFormat="1" ht="250.65" customHeight="1" spans="1:20">
       <c r="A12" s="12">
-        <v>46053</v>
+        <v>46071</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14">
-        <v>70000</v>
+        <v>240000</v>
       </c>
       <c r="E12" s="19">
         <f t="shared" si="0"/>
-        <v>1903845</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>42</v>
+        <v>1846978</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>39</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="4"/>
@@ -3537,27 +3149,27 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
     </row>
-    <row r="13" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
+    <row r="13" customFormat="1" ht="263.9" customHeight="1" spans="1:20">
       <c r="A13" s="12">
-        <v>46053</v>
+        <v>46071</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14">
-        <v>64000</v>
+        <v>62500</v>
       </c>
       <c r="E13" s="19">
         <f t="shared" si="0"/>
-        <v>1839845</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>44</v>
+        <v>1784478</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="4"/>
@@ -3571,166 +3183,129 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
     </row>
-    <row r="14" customFormat="1" ht="190.45" customHeight="1" spans="1:20">
+    <row r="14" customFormat="1" ht="397.3" customHeight="1" spans="1:20">
       <c r="A14" s="12">
-        <v>46053</v>
+        <v>46073</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14">
-        <v>87000</v>
+        <v>66300</v>
       </c>
       <c r="E14" s="19">
         <f t="shared" si="0"/>
-        <v>1752845</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>45</v>
+        <v>1718178</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="44">
-        <f>SUMIFS(D:D,H:H,"F",A:A,S14,A:A,T14)</f>
-        <v>915000</v>
-      </c>
-      <c r="L14" s="44">
-        <f>SUMIFS(D:D,H:H,"B",A:A,S14,A:A,T14)</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="44">
-        <f>SUMIFS(D:D,H:H,"K",A:A,S14,A:A,T14)</f>
-        <v>1071897</v>
-      </c>
-      <c r="N14" s="52">
-        <f>SUMIFS(D:D,H:H,"S",A:A,S14,A:A,T14)</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="52">
-        <f>SUMIFS(D:D,H:H,"M",A:A,S14,A:A,T14)-SUMIFS(C:C,H:H,"M",A:A,S14,A:A,T14)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="52">
-        <f>SUMIFS(C:C,H:H,"T",A:A,S14,A:A,T14)-SUMIFS(D:D,H:H,"T",A:A,S14,A:A,T14)</f>
-        <v>2934800</v>
-      </c>
-      <c r="Q14" s="52">
-        <f>SUMIFS(C:C,H:H,"I",A:A,S14,A:A,T14)</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="S14" s="22" t="str">
-        <f>"&gt;="&amp;DATE(2026,1,1)</f>
-        <v>&gt;=46023</v>
-      </c>
-      <c r="T14" s="56" t="str">
-        <f>"&lt;="&amp;DATE(2026,1,31)</f>
-        <v>&lt;=46053</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
     </row>
-    <row r="15" customFormat="1" ht="274.4" customHeight="1" spans="1:22">
+    <row r="15" customFormat="1" ht="279.85" customHeight="1" spans="1:20">
       <c r="A15" s="12">
-        <v>46054</v>
+        <v>46073</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14">
-        <v>20142</v>
+        <v>70000</v>
       </c>
       <c r="E15" s="19">
         <f t="shared" si="0"/>
-        <v>1732703</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>49</v>
+        <v>1648178</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="45"/>
+        <v>31</v>
+      </c>
+      <c r="J15" s="3"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="O15" s="3"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="3"/>
-      <c r="T15"/>
-      <c r="U15" s="59"/>
-      <c r="V15" s="59"/>
+      <c r="T15" s="3"/>
     </row>
-    <row r="16" customFormat="1" ht="108.5" customHeight="1" spans="1:20">
+    <row r="16" customFormat="1" ht="264.8" customHeight="1" spans="1:20">
       <c r="A16" s="12">
-        <v>46055</v>
+        <v>46073</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14">
-        <v>102500</v>
+        <v>182000</v>
       </c>
       <c r="E16" s="19">
         <f t="shared" si="0"/>
-        <v>1630203</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>50</v>
+        <v>1466178</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>45</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="58"/>
+        <v>31</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
     </row>
-    <row r="17" customFormat="1" ht="111.35" customHeight="1" spans="1:20">
+    <row r="17" customFormat="1" ht="199.4" customHeight="1" spans="1:20">
       <c r="A17" s="12">
-        <v>46056</v>
+        <v>46073</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14">
-        <v>149020</v>
+        <v>193120</v>
       </c>
       <c r="E17" s="19">
         <f t="shared" si="0"/>
-        <v>1481183</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>51</v>
+        <v>1273058</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>47</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="22" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="4"/>
@@ -3744,27 +3319,27 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
     </row>
-    <row r="18" customFormat="1" ht="287.75" customHeight="1" spans="1:20">
+    <row r="18" customFormat="1" ht="397.65" customHeight="1" spans="1:20">
       <c r="A18" s="12">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14">
-        <v>76600</v>
+        <v>23500</v>
       </c>
       <c r="E18" s="19">
         <f t="shared" si="0"/>
-        <v>1404583</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>53</v>
+        <v>1249558</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>49</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="4"/>
@@ -3778,27 +3353,27 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
     </row>
-    <row r="19" customFormat="1" ht="100.95" customHeight="1" spans="1:20">
+    <row r="19" customFormat="1" ht="331.2" customHeight="1" spans="1:20">
       <c r="A19" s="12">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14">
-        <v>149020</v>
+        <v>24500</v>
       </c>
       <c r="E19" s="19">
         <f t="shared" si="0"/>
-        <v>1255563</v>
-      </c>
-      <c r="F19" s="30" t="s">
-        <v>54</v>
+        <v>1225058</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>51</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="22" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="4"/>
@@ -3812,27 +3387,27 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" customFormat="1" ht="319.5" customHeight="1" spans="1:20">
+    <row r="20" customFormat="1" ht="230.3" customHeight="1" spans="1:20">
       <c r="A20" s="12">
-        <v>46059</v>
+        <v>46075</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14">
-        <v>48000</v>
+        <v>32500</v>
       </c>
       <c r="E20" s="19">
         <f t="shared" si="0"/>
-        <v>1207563</v>
-      </c>
-      <c r="F20" s="30" t="s">
-        <v>56</v>
+        <v>1192558</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>53</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="22" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="4"/>
@@ -3846,23 +3421,23 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" customFormat="1" ht="229.55" customHeight="1" spans="1:20">
+    <row r="21" customFormat="1" ht="396.45" customHeight="1" spans="1:20">
       <c r="A21" s="12">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14">
-        <v>108000</v>
+        <v>52500</v>
       </c>
       <c r="E21" s="19">
         <f t="shared" si="0"/>
-        <v>1099563</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>58</v>
+        <v>1140058</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>55</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="22" t="s">
@@ -3880,23 +3455,23 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
     </row>
-    <row r="22" customFormat="1" ht="260.1" customHeight="1" spans="1:20">
+    <row r="22" customFormat="1" ht="398.55" customHeight="1" spans="1:20">
       <c r="A22" s="12">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14">
-        <v>263000</v>
+        <v>381970</v>
       </c>
       <c r="E22" s="19">
         <f t="shared" si="0"/>
-        <v>836563</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>60</v>
+        <v>758088</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="22" t="s">
@@ -3914,62 +3489,61 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23" customFormat="1" ht="233.15" customHeight="1" spans="1:20">
+    <row r="23" customFormat="1" ht="389.7" customHeight="1" spans="1:20">
       <c r="A23" s="12">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14">
-        <v>252500</v>
+        <v>64500</v>
       </c>
       <c r="E23" s="19">
         <f t="shared" si="0"/>
-        <v>584063</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>62</v>
+        <v>693588</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>58</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="57"/>
-      <c r="T23" s="58"/>
+        <v>27</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
     </row>
-    <row r="24" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
+    <row r="24" customFormat="1" ht="337.5" customHeight="1" spans="1:20">
       <c r="A24" s="12">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="14">
-        <v>76600</v>
-      </c>
-      <c r="D24" s="14"/>
+        <v>59</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14">
+        <v>54500</v>
+      </c>
       <c r="E24" s="19">
-        <f t="shared" ref="E24:E60" si="1">E23+C24-D24</f>
-        <v>660663</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>64</v>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>60</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="22" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="4"/>
@@ -3983,28 +3557,18 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
     </row>
-    <row r="25" customFormat="1" ht="244.85" customHeight="1" spans="1:20">
-      <c r="A25" s="12">
-        <v>46060</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>65</v>
-      </c>
+    <row r="25" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="14"/>
-      <c r="D25" s="14">
-        <v>58000</v>
-      </c>
+      <c r="D25" s="14"/>
       <c r="E25" s="19">
-        <f t="shared" si="1"/>
-        <v>602663</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="21"/>
-      <c r="H25" s="22" t="s">
-        <v>27</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="22"/>
       <c r="J25" s="3"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -4017,28 +3581,18 @@
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" customFormat="1" ht="263.5" customHeight="1" spans="1:20">
-      <c r="A26" s="12">
-        <v>46060</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>67</v>
-      </c>
+    <row r="26" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="14">
-        <v>12500</v>
-      </c>
+      <c r="D26" s="14"/>
       <c r="E26" s="19">
-        <f t="shared" si="1"/>
-        <v>590163</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22" t="s">
-        <v>27</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="22"/>
       <c r="J26" s="3"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -4051,98 +3605,66 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
     </row>
-    <row r="27" customFormat="1" ht="238.85" customHeight="1" spans="1:20">
-      <c r="A27" s="12">
-        <v>46060</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>69</v>
-      </c>
+    <row r="27" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="14">
-        <v>42500</v>
-      </c>
+      <c r="D27" s="14"/>
       <c r="E27" s="19">
-        <f t="shared" si="1"/>
-        <v>547663</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" s="47"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="57"/>
-      <c r="T27" s="58"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="22"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
     </row>
-    <row r="28" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
-      <c r="A28" s="12">
-        <v>46061</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="28" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="14">
-        <v>167500</v>
-      </c>
+      <c r="D28" s="14"/>
       <c r="E28" s="19">
-        <f t="shared" si="1"/>
-        <v>380163</v>
-      </c>
-      <c r="F28" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="47"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="57"/>
-      <c r="T28" s="58"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="22"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
     </row>
-    <row r="29" customFormat="1" ht="409.5" customHeight="1" spans="1:20">
-      <c r="A29" s="12">
-        <v>46063</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>23</v>
-      </c>
+    <row r="29" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="14">
-        <v>149020</v>
-      </c>
+      <c r="D29" s="14"/>
       <c r="E29" s="19">
-        <f t="shared" si="1"/>
-        <v>231143</v>
-      </c>
-      <c r="F29" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22" t="s">
-        <v>22</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="22"/>
       <c r="J29" s="3"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -4155,28 +3677,18 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
     </row>
-    <row r="30" customFormat="1" ht="112" customHeight="1" spans="1:20">
-      <c r="A30" s="12">
-        <v>46063</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>23</v>
-      </c>
+    <row r="30" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
       <c r="C30" s="14"/>
-      <c r="D30" s="14">
-        <v>149020</v>
-      </c>
+      <c r="D30" s="14"/>
       <c r="E30" s="19">
-        <f t="shared" si="1"/>
-        <v>82123</v>
-      </c>
-      <c r="F30" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22" t="s">
-        <v>22</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="22"/>
       <c r="J30" s="3"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -4189,28 +3701,18 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
     </row>
-    <row r="31" customFormat="1" ht="203.65" customHeight="1" spans="1:20">
-      <c r="A31" s="12">
-        <v>46063</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>41</v>
-      </c>
+    <row r="31" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="14"/>
-      <c r="D31" s="14">
-        <v>70000</v>
-      </c>
+      <c r="D31" s="14"/>
       <c r="E31" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22" t="s">
-        <v>27</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="22"/>
       <c r="J31" s="3"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -4229,11 +3731,11 @@
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="34"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
       <c r="H32" s="22"/>
       <c r="J32" s="3"/>
       <c r="K32" s="4"/>
@@ -4253,11 +3755,11 @@
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
       <c r="E33" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="34"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="30"/>
       <c r="H33" s="22"/>
       <c r="J33" s="3"/>
       <c r="K33" s="4"/>
@@ -4277,11 +3779,11 @@
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="34"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="30"/>
       <c r="H34" s="22"/>
       <c r="J34" s="3"/>
       <c r="K34" s="4"/>
@@ -4301,11 +3803,11 @@
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="34"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F35" s="29"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="22"/>
       <c r="J35" s="3"/>
       <c r="K35" s="4"/>
@@ -4325,11 +3827,11 @@
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
       <c r="E36" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="34"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="30"/>
       <c r="H36" s="22"/>
       <c r="J36" s="3"/>
       <c r="K36" s="4"/>
@@ -4349,11 +3851,11 @@
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
       <c r="E37" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="34"/>
+        <f t="shared" si="0"/>
+        <v>639088</v>
+      </c>
+      <c r="F37" s="29"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="22"/>
       <c r="J37" s="3"/>
       <c r="K37" s="4"/>
@@ -4367,592 +3869,86 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
     </row>
-    <row r="38" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
+    <row r="38" customFormat="1" ht="51.2" spans="1:20">
       <c r="A38" s="12"/>
       <c r="B38" s="13"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
+        <f t="shared" si="0"/>
+        <v>639088</v>
       </c>
       <c r="F38" s="31"/>
-      <c r="G38" s="34"/>
+      <c r="G38" s="30"/>
       <c r="H38" s="22"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
-    </row>
-    <row r="39" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F39" s="31"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="22"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-    </row>
-    <row r="40" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="22"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-    </row>
-    <row r="41" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="22"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-    </row>
-    <row r="42" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="22"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-    </row>
-    <row r="43" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F43" s="31"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="22"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-    </row>
-    <row r="44" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F44" s="31"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="22"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
-    </row>
-    <row r="45" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F45" s="31"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="22"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-    </row>
-    <row r="46" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="22"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-    </row>
-    <row r="47" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F47" s="31"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="22"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-    </row>
-    <row r="48" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F48" s="31"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="22"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-    </row>
-    <row r="49" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F49" s="31"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="22"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-    </row>
-    <row r="50" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F50" s="31"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="22"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-    </row>
-    <row r="51" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F51" s="31"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="22"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-    </row>
-    <row r="52" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A52" s="12"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="22"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-    </row>
-    <row r="53" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A53" s="12"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F53" s="31"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="22"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
-      <c r="R53" s="5"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-    </row>
-    <row r="54" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A54" s="12"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F54" s="31"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="22"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="5"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-    </row>
-    <row r="55" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A55" s="12"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F55" s="31"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="22"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="5"/>
-      <c r="R55" s="5"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-    </row>
-    <row r="56" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A56" s="12"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F56" s="31"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="22"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="5"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
-    </row>
-    <row r="57" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A57" s="12"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F57" s="31"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="22"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="5"/>
-      <c r="Q57" s="5"/>
-      <c r="R57" s="5"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-    </row>
-    <row r="58" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F58" s="31"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="22"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="5"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
-    </row>
-    <row r="59" customFormat="1" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A59" s="12"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F59" s="31"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="22"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="5"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="5"/>
-      <c r="Q59" s="5"/>
-      <c r="R59" s="5"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-    </row>
-    <row r="60" customFormat="1" ht="51.2" spans="1:20">
-      <c r="A60" s="12"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="19">
-        <f t="shared" si="1"/>
-        <v>12123</v>
-      </c>
-      <c r="F60" s="35"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="42" t="s">
+      <c r="I38" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="K60" s="44">
-        <f>SUMIFS(D:D,H:H,"F",A:A,S60,A:A,T60)</f>
-        <v>650742</v>
-      </c>
-      <c r="L60" s="44">
-        <f>SUMIFS(D:D,H:H,"B",A:A,S60,A:A,T60)</f>
-        <v>252500</v>
-      </c>
-      <c r="M60" s="44">
-        <f>SUMIFS(D:D,H:H,"K",A:A,S60,A:A,T60)</f>
-        <v>914080</v>
-      </c>
-      <c r="N60" s="52">
-        <f>SUMIFS(D:D,H:H,"S",A:A,S60,A:A,T60)</f>
+      <c r="J38" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="K38" s="40">
+        <f>SUMIFS(D:D,H:H,"F",A:A,S38,A:A,T38)</f>
+        <v>831005</v>
+      </c>
+      <c r="L38" s="41">
+        <f>SUMIFS(D:D,H:H,"B",A:A,S38,A:A,T38)</f>
+        <v>293120</v>
+      </c>
+      <c r="M38" s="47">
+        <f>SUMIFS(D:D,H:H,"K",A:A,S38,A:A,T38)</f>
+        <v>1289730</v>
+      </c>
+      <c r="N38" s="48">
+        <f>SUMIFS(D:D,H:H,"S",A:A,S38,A:A,T38)</f>
         <v>0</v>
       </c>
-      <c r="O60" s="52">
-        <f>SUMIFS(D:D,H:H,"M",A:A,S60,A:A,T60)-SUMIFS(C:C,H:H,"M",A:A,S60,A:A,T60)</f>
+      <c r="O38" s="49">
+        <f>SUMIFS(D:D,H:H,"M",A:A,S38,A:A,T38)-SUMIFS(C:C,H:H,"M",A:A,S38,A:A,T38)</f>
         <v>0</v>
       </c>
-      <c r="P60" s="52">
-        <f>SUMIFS(C:C,H:H,"T",A:A,S60,A:A,T60)-SUMIFS(D:D,H:H,"T",A:A,S60,A:A,T60)</f>
-        <v>76600</v>
-      </c>
-      <c r="Q60" s="52">
-        <f>SUMIFS(C:C,H:H,"I",A:A,S60,A:A,T60)</f>
+      <c r="P38" s="50">
+        <f>SUMIFS(C:C,H:H,"T",A:A,S38,A:A,T38)-SUMIFS(D:D,H:H,"T",A:A,S38,A:A,T38)</f>
+        <v>2998800</v>
+      </c>
+      <c r="Q38" s="53">
+        <f>SUMIFS(C:C,H:H,"I",A:A,S38,A:A,T38)</f>
         <v>0</v>
       </c>
-      <c r="R60" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="S60" s="22" t="str">
+      <c r="R38" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="S38" s="22" t="str">
         <f>"&gt;="&amp;DATE(2026,2,1)</f>
         <v>&gt;=46054</v>
       </c>
-      <c r="T60" s="56" t="str">
+      <c r="T38" s="54" t="str">
         <f>"&lt;="&amp;DATE(2026,2,31)</f>
         <v>&lt;=46084</v>
       </c>
     </row>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
     <row r="61" ht="15.75" customHeight="1"/>
     <row r="62" ht="15.75" customHeight="1"/>
     <row r="63" ht="15.75" customHeight="1"/>
@@ -5683,28 +4679,6 @@
     <row r="788" ht="15.75" customHeight="1"/>
     <row r="789" ht="15.75" customHeight="1"/>
     <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:A2"/>
@@ -5714,7 +4688,7 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
   </mergeCells>
